--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5721CC84-DEF5-4B48-BB7A-BC5308D3A876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F991E8F-2030-400E-9719-FEFA4C61F94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Massa_HML_B31_FLUXO_INTEGRADO" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="69">
   <si>
     <t>CPF</t>
   </si>
@@ -128,17 +128,9 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria "Segurado especial" onde o parâmetro "Exige Autodeclaração" no Catálogo está ATIVADO e foi respondida a autodeclaração COM período pendente
-**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ</t>
-  </si>
-  <si>
     <t>PAT</t>
   </si>
   <si>
-    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria "Segurado especial" onde o parâmetro "Exige Autodeclaração" no Catálogo está ATIVADO e foi respondida a autodeclaração SEM período pendente
-**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ</t>
-  </si>
-  <si>
     <t>Cumprir a exigência de autodeclaração</t>
   </si>
   <si>
@@ -148,109 +140,160 @@
     <t>Responder o formulário de autodeclaração acessando diretamente a aba segurado especial ao detalhar a tarefa, onde a tarefa encontra-se em exigência de documento médico</t>
   </si>
   <si>
-    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria "Segurado especial" onde o parâmetro "Exige Autodeclaração" no Catálogo está ATIVADO,  NÃO foi respondida a autodeclaração, NÃO foi incluído o anexo detalhado de AD e cidadão está preso
-**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria "Segurado especial" onde o parâmetro "Exige Autodeclaração" no Catálogo está ATIVADO,  NÃO foi respondida a autodeclaração, NÃO foi incluído o anexo detalhado de AD e cidadão ficou sem trabalhar
-**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ</t>
-  </si>
-  <si>
-    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria "Segurado especial" onde o parâmetro "Exige Autodeclaração" no Catálogo está ATIVADO,  NÃO foi respondida a autodeclaração e foi incluído o anexo detalhado de AD
-**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ</t>
-  </si>
-  <si>
-    <t>Criar tarefa de BI inicial fluxo PRESENCIAL para categoria "Segurado especial" onde o parâmetro "Exige Autodeclaração" no Catálogo está ATIVADO, NÃO foi respondida a autodeclaração e NÃO foi incluído o anexo detalhado de AD
+    <t>Responder o formulário de autodeclaração acionando a opção de autodeclaração no card do pedido onde a tarefa encontra-se em exigência de documento médico
+Será posível acessar diretamente a autodeclaração logado no Meu INSS?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STATUS </t>
+  </si>
+  <si>
+    <t>AG CORRREÇÃO</t>
+  </si>
+  <si>
+    <t>APROVADO</t>
+  </si>
+  <si>
+    <t>REPROVADO</t>
+  </si>
+  <si>
+    <t>AG RETESTE</t>
+  </si>
+  <si>
+    <t>NÃO EXECUTADO</t>
+  </si>
+  <si>
+    <t>EM TESTE</t>
+  </si>
+  <si>
+    <t>Hora</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>Não Executado</t>
+  </si>
+  <si>
+    <t>Aprovados</t>
+  </si>
+  <si>
+    <t>Ag Corração</t>
+  </si>
+  <si>
+    <t>Em Execução</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO e foi respondida a autodeclaração COM período pendente
+**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ"</t>
+  </si>
+  <si>
+    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO e foi respondida a autodeclaração SEM período pendente
+**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ"</t>
+  </si>
+  <si>
+    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO,  NÃO foi respondida a autodeclaração, NÃO foi incluído o anexo detalhado de AD e cidadão está preso
+**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ"</t>
+  </si>
+  <si>
+    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO,  NÃO foi respondida a autodeclaração, NÃO foi incluído o anexo detalhado de AD e cidadão ficou sem trabalhar
+**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ"</t>
+  </si>
+  <si>
+    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO,  NÃO foi respondida a autodeclaração e foi incluído o anexo detalhado de AD
+**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ"</t>
+  </si>
+  <si>
+    <t>Criar tarefa de BI inicial fluxo PRESENCIAL para categoria ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO, NÃO foi respondida a autodeclaração e NÃO foi incluído o anexo detalhado de AD
+**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ
+**Parâmetro PAT ligado: 109 -Tipo de Incapacidade Permanente leva à Fluxo Presencial do Novo BI"</t>
+  </si>
+  <si>
+    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria diferente de ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO
+**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ"</t>
+  </si>
+  <si>
+    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO e a autodeclaração tem período pendente
+**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ"</t>
+  </si>
+  <si>
+    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO e foi respondida a autodeclaração sem período pendente
+**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ"</t>
+  </si>
+  <si>
+    <t>Responder o formulário de autodeclaração acessando diretamente a aba segurado especial ao detalhar a tarefa, onde a tarefa encontra-se em exigência de documento médico
+Será posível acessar diretamente a autodeclaração logado como EC?"</t>
+  </si>
+  <si>
+    <t>Criar tarefa de BI inicial fluxo PRESENCIAL para categoria diferente de ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO
 **Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ
 **Parâmetro PAT ligado: 109 -Tipo de Incapacidade Permanente leva à Fluxo Presencial do Novo BI</t>
   </si>
   <si>
-    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria "Segurado especial" onde o parâmetro "Exige Autodeclaração" no Catálogo está ATIVADO e a autodeclaração tem período pendente
+    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO e foi respondida a autodeclaração com período pendente
 **Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ</t>
   </si>
   <si>
-    <t>Entidade Conveniada</t>
-  </si>
-  <si>
-    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria "Segurado especial" onde o parâmetro "Exige Autodeclaração" no Catálogo está ATIVADO e foi respondida a autodeclaração sem período pendente
+    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO e foi respondida a autodeclaração sem período pendente
 **Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ</t>
   </si>
   <si>
-    <t>Responder o formulário de autodeclaração acessando diretamente a aba segurado especial ao detalhar a tarefa, onde a tarefa encontra-se em exigência de documento médico
-Será posível acessar diretamente a autodeclaração logado como EC?</t>
-  </si>
-  <si>
-    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria "Segurado especial" onde o parâmetro "Exige Autodeclaração" no Catálogo está ATIVADO e foi respondida a autodeclaração com período pendente
+    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO e  NÃO foi respondida a autodeclaração
 **Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ</t>
   </si>
   <si>
-    <t>MEU INSS</t>
-  </si>
-  <si>
     <t>Responder o formulário de autodeclaração acionando a opção de autodeclaração no card do pedido onde a tarefa encontra-se em exigência de autodeclaração
-Será posível acessar diretamente a autodeclaração logado no Meu INSS?</t>
-  </si>
-  <si>
-    <t>Responder o formulário de autodeclaração acionando a opção de autodeclaração no card do pedido onde a tarefa encontra-se em exigência de documento médico
-Será posível acessar diretamente a autodeclaração logado no Meu INSS?</t>
-  </si>
-  <si>
-    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria "Segurado especial" onde o parâmetro "Exige Autodeclaração" no Catálogo está ATIVADO,  foi respondida a autodeclaração, NÃO foi incluído o anexo detalhado de AD e ocorreu enquadramento na regra da análise de risco
+Será posível acessar diretamente a autodeclaração logado no Meu INSS?"</t>
+  </si>
+  <si>
+    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO,  foi respondida a autodeclaração, NÃO foi incluído o anexo detalhado de AD e ocorreu enquadramento na regra da análise de risco
 **Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ
 **Parâmetro PAT ligado: 119 - Habilitar fluxo de Análise de Risco no Novo BI</t>
   </si>
   <si>
-    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria "Segurado especial" onde o parâmetro "Exige Autodeclaração" no Catálogo está ATIVADO, NÃO foi respondida a autodeclaração, NÃO foi incluído o anexo detalhado de AD e ocorreu enquadramento na regra da análise de risco
+    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria ""Segurado especial"" onde o parâmetro ""Exige Autodeclaração"" no Catálogo está ATIVADO, NÃO foi respondida a autodeclaração, NÃO foi incluído o anexo detalhado de AD e ocorreu enquadramento na regra da análise de risco
 **Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ
 **Parâmetro PAT ligado: 119 - Habilitar fluxo de Análise de Risco no Novo BI</t>
   </si>
   <si>
-    <t>Criar tarefa de BI inicial fluxo ATESTMEDQ para categoria "Segurado especial" onde o parâmetro "Exige Autodeclaração" no Catálogo está ATIVADO, NÃO foi respondida a autodeclaração, NÃO foi incluído o anexo detalhado de AD e ocorreu enquadramento na regra da análise de risco
-**Parâmetro PAT ligado: 144 - Fluxo ATESTMEDQ
-**Parâmetro PAT ligado: 119 - Habilitar fluxo de Análise de Risco no Novo BI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STATUS </t>
-  </si>
-  <si>
-    <t>AG CORRREÇÃO</t>
-  </si>
-  <si>
-    <t>APROVADO</t>
-  </si>
-  <si>
-    <t>REPROVADO</t>
-  </si>
-  <si>
-    <t>AG RETESTE</t>
-  </si>
-  <si>
-    <t>NÃO EXECUTADO</t>
-  </si>
-  <si>
-    <t>EM TESTE</t>
-  </si>
-  <si>
-    <t>Hora</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Não Executado</t>
-  </si>
-  <si>
-    <t>Aprovados</t>
-  </si>
-  <si>
-    <t>Ag Corração</t>
-  </si>
-  <si>
-    <t>Em Execução</t>
-  </si>
-  <si>
-    <t>Total</t>
+    <t>Central 135</t>
+  </si>
+  <si>
+    <t>EC</t>
+  </si>
+  <si>
+    <t>Meu INSS</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Criação de tarefa de BI inicial com fluxo ATESTMED para categoria DIFERENTE de Segurado Especial COM exigência de preenchimento da AD.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Premissas:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Catálogo: Exige autodeclaração = ATIVADO
+Parâmetro:  144 - Fluxo ATESTMED = LIGADO</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -411,7 +454,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -603,8 +646,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -762,6 +823,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -807,7 +881,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -821,9 +895,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
@@ -841,6 +912,42 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1207,7 +1314,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834A0C64-4F07-424E-993E-2EA5E6BA9836}">
-  <dimension ref="A1:F267"/>
+  <dimension ref="A1:F266"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -1255,38 +1362,42 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="21">
         <v>848157362</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1" t="s">
-        <v>8</v>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>938209337</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1" t="s">
+      <c r="A4" s="21">
+        <v>20673310</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
-        <v>20673310</v>
+        <v>21376310</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
@@ -1301,40 +1412,44 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>21376310</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="4" t="s">
+      <c r="A6" s="21">
+        <v>40322335</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1" t="s">
-        <v>8</v>
+      <c r="E6" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>40322335</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
-        <v>8</v>
+      <c r="A7" s="21">
+        <v>2734924625</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>2734924625</v>
+        <v>3596776490</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
@@ -1350,37 +1465,39 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>3596776490</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="4" t="s">
-        <v>10</v>
-      </c>
+        <v>4234381667</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="4"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>4234381667</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
-        <v>8</v>
+      <c r="A10" s="21">
+        <v>9220661837</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>9220661837</v>
+        <v>9293815990</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
@@ -1396,7 +1513,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>9293815990</v>
+        <v>14810271153</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
@@ -1412,14 +1529,14 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>14810271153</v>
+        <v>34866868368</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1" t="s">
@@ -1428,7 +1545,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>34866868368</v>
+        <v>61902037367</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
@@ -1444,7 +1561,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
-        <v>61902037367</v>
+        <v>73620963649</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
@@ -1460,14 +1577,14 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
-        <v>73620963649</v>
+        <v>94332096991</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1" t="s">
@@ -1476,14 +1593,14 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
-        <v>94332096991</v>
+        <v>99894300391</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1" t="s">
@@ -1492,14 +1609,14 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
-        <v>99894300391</v>
+        <v>737185309</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1" t="s">
@@ -1508,14 +1625,12 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
-        <v>737185309</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>1304390373</v>
+      </c>
+      <c r="B19" s="1"/>
       <c r="C19" s="1"/>
       <c r="D19" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1" t="s">
@@ -1524,12 +1639,14 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
-        <v>1304390373</v>
-      </c>
-      <c r="B20" s="1"/>
+        <v>2185404938</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C20" s="1"/>
       <c r="D20" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
@@ -1538,15 +1655,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>2185404938</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="4" t="s">
-        <v>7</v>
-      </c>
+        <v>4024368818</v>
+      </c>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="4"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
         <v>8</v>
@@ -1554,13 +1669,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
-        <v>4024368818</v>
+        <v>5136194960</v>
       </c>
       <c r="B22" s="1"/>
-      <c r="C22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="4"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
         <v>8</v>
@@ -1568,12 +1683,14 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
-        <v>5136194960</v>
-      </c>
-      <c r="B23" s="1"/>
+        <v>5863603526</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C23" s="1"/>
       <c r="D23" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1" t="s">
@@ -1582,7 +1699,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
-        <v>5863603526</v>
+        <v>12401303685</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
@@ -1598,7 +1715,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
-        <v>12401303685</v>
+        <v>44771380597</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
@@ -1614,14 +1731,14 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
-        <v>44771380597</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="1"/>
+        <v>3179868996</v>
+      </c>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D26" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1" t="s">
@@ -1630,14 +1747,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
-        <v>3179868996</v>
-      </c>
-      <c r="B27" s="1"/>
+        <v>8707937563</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C27" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1" t="s">
@@ -1646,7 +1765,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
-        <v>8707937563</v>
+        <v>10062959417</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>6</v>
@@ -1664,16 +1783,14 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
-        <v>10062959417</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>15477671467</v>
+      </c>
+      <c r="B29" s="1"/>
       <c r="C29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="s">
@@ -1682,7 +1799,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
-        <v>15477671467</v>
+        <v>17713986987</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
@@ -1698,7 +1815,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
-        <v>17713986987</v>
+        <v>20404965806</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
@@ -1714,15 +1831,13 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
-        <v>20404965806</v>
+        <v>33629307000</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="D32" s="4"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1" t="s">
         <v>8</v>
@@ -1730,9 +1845,11 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
-        <v>33629307000</v>
-      </c>
-      <c r="B33" s="1"/>
+        <v>68136811091</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C33" s="1" t="s">
         <v>6</v>
       </c>
@@ -1744,7 +1861,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
-        <v>68136811091</v>
+        <v>83002812153</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>6</v>
@@ -1752,7 +1869,9 @@
       <c r="C34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D34" s="4"/>
+      <c r="D34" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1" t="s">
         <v>8</v>
@@ -1760,7 +1879,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
-        <v>83002812153</v>
+        <v>85179817315</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>6</v>
@@ -1769,7 +1888,7 @@
         <v>6</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1" t="s">
@@ -1778,16 +1897,14 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
-        <v>85179817315</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>87764997404</v>
+      </c>
+      <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
@@ -1796,12 +1913,12 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
-        <v>87764997404</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>3710335</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="1"/>
       <c r="D37" s="4" t="s">
         <v>10</v>
       </c>
@@ -1812,7 +1929,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
-        <v>3710335</v>
+        <v>6787240</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>6</v>
@@ -1828,7 +1945,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
-        <v>6787240</v>
+        <v>9366261</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>6</v>
@@ -1844,7 +1961,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
-        <v>9366261</v>
+        <v>1548301</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>6</v>
@@ -1860,7 +1977,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
-        <v>1548301</v>
+        <v>1818384</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>6</v>
@@ -1876,14 +1993,14 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
-        <v>1818384</v>
+        <v>59054271</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1" t="s">
@@ -1892,7 +2009,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
-        <v>59054271</v>
+        <v>65913299</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>6</v>
@@ -1908,14 +2025,14 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
-        <v>65913299</v>
+        <v>79277209</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1" t="s">
@@ -1924,14 +2041,12 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
-        <v>79277209</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>79682219</v>
+      </c>
+      <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1" t="s">
@@ -1940,7 +2055,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>79682219</v>
+        <v>102850240</v>
       </c>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -1954,12 +2069,14 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
-        <v>102850240</v>
-      </c>
-      <c r="B47" s="1"/>
+        <v>114745218</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C47" s="1"/>
       <c r="D47" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1" t="s">
@@ -1968,14 +2085,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
-        <v>114745218</v>
+        <v>7227906</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="1"/>
+      <c r="C48" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D48" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1" t="s">
@@ -1984,17 +2103,13 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
-        <v>7227906</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>9427660</v>
+      </c>
+      <c r="B49" s="1"/>
       <c r="C49" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="D49" s="4"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1" t="s">
         <v>8</v>
@@ -2002,13 +2117,17 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
-        <v>9427660</v>
-      </c>
-      <c r="B50" s="1"/>
+        <v>10152148</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C50" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D50" s="4"/>
+      <c r="D50" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1" t="s">
         <v>8</v>
@@ -2016,7 +2135,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
-        <v>10152148</v>
+        <v>61461121</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>6</v>
@@ -2034,7 +2153,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
-        <v>61461121</v>
+        <v>93573006</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>6</v>
@@ -2042,9 +2161,7 @@
       <c r="C52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D52" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="D52" s="4"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1" t="s">
         <v>8</v>
@@ -2052,7 +2169,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
-        <v>93573006</v>
+        <v>95026100</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>6</v>
@@ -2068,7 +2185,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
-        <v>95026100</v>
+        <v>7494173404</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>6</v>
@@ -2076,7 +2193,9 @@
       <c r="C54" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D54" s="4"/>
+      <c r="D54" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1" t="s">
         <v>8</v>
@@ -2084,7 +2203,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
-        <v>7494173404</v>
+        <v>7496954390</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>6</v>
@@ -2093,7 +2212,7 @@
         <v>6</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1" t="s">
@@ -2102,7 +2221,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
-        <v>7496954390</v>
+        <v>7502772383</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>6</v>
@@ -2120,16 +2239,12 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
-        <v>7502772383</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>234346</v>
+      </c>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
       <c r="D57" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1" t="s">
@@ -2138,12 +2253,14 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
-        <v>234346</v>
-      </c>
-      <c r="B58" s="1"/>
+        <v>251275</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C58" s="1"/>
       <c r="D58" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1" t="s">
@@ -2152,14 +2269,14 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
-        <v>251275</v>
+        <v>40999408</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1" t="s">
@@ -2168,14 +2285,12 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
-        <v>40999408</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>52062511</v>
+      </c>
+      <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="4" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1" t="s">
@@ -2184,12 +2299,14 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
-        <v>52062511</v>
-      </c>
-      <c r="B61" s="1"/>
+        <v>96619309</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C61" s="1"/>
       <c r="D61" s="4" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1" t="s">
@@ -2198,15 +2315,13 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
-        <v>96619309</v>
+        <v>2184685550</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C62" s="1"/>
-      <c r="D62" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="D62" s="4"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1" t="s">
         <v>8</v>
@@ -2214,13 +2329,17 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
-        <v>2184685550</v>
+        <v>136679390</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C63" s="1"/>
-      <c r="D63" s="4"/>
+      <c r="C63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1" t="s">
         <v>8</v>
@@ -2228,7 +2347,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
-        <v>136679390</v>
+        <v>284905330</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>6</v>
@@ -2236,9 +2355,7 @@
       <c r="C64" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="D64" s="4"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1" t="s">
         <v>8</v>
@@ -2246,7 +2363,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
-        <v>284905330</v>
+        <v>404822606</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>6</v>
@@ -2254,7 +2371,9 @@
       <c r="C65" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D65" s="4"/>
+      <c r="D65" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1" t="s">
         <v>8</v>
@@ -2262,7 +2381,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
-        <v>404822606</v>
+        <v>455785163</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>6</v>
@@ -2280,11 +2399,9 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
-        <v>455785163</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>485318989</v>
+      </c>
+      <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
         <v>6</v>
       </c>
@@ -2298,15 +2415,13 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
-        <v>485318989</v>
-      </c>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>10</v>
-      </c>
+        <v>98983768304</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="1"/>
+      <c r="D68" s="4"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1" t="s">
         <v>8</v>
@@ -2314,13 +2429,15 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
-        <v>98983768304</v>
+        <v>99052210349</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C69" s="1"/>
-      <c r="D69" s="4"/>
+      <c r="D69" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1" t="s">
         <v>8</v>
@@ -2328,14 +2445,12 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
-        <v>99052210349</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>99178826500</v>
+      </c>
+      <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1" t="s">
@@ -2344,12 +2459,14 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
-        <v>99178826500</v>
-      </c>
-      <c r="B71" s="1"/>
+        <v>99447444504</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C71" s="1"/>
       <c r="D71" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1" t="s">
@@ -2358,15 +2475,13 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
-        <v>99447444504</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="D72" s="4" t="s">
-        <v>10</v>
-      </c>
+        <v>541253913</v>
+      </c>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" s="4"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1" t="s">
         <v>8</v>
@@ -2374,13 +2489,17 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
-        <v>541253913</v>
-      </c>
-      <c r="B73" s="1"/>
+        <v>583695540</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C73" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D73" s="4"/>
+      <c r="D73" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1" t="s">
         <v>8</v>
@@ -2388,7 +2507,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
-        <v>583695540</v>
+        <v>887361307</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>6</v>
@@ -2397,7 +2516,7 @@
         <v>6</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E74" s="1"/>
       <c r="F74" s="1" t="s">
@@ -2406,7 +2525,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
-        <v>887361307</v>
+        <v>979170796</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>6</v>
@@ -2424,7 +2543,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
-        <v>979170796</v>
+        <v>1017978506</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>6</v>
@@ -2442,17 +2561,13 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
-        <v>1017978506</v>
+        <v>94893438549</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="C77" s="1"/>
+      <c r="D77" s="4"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1" t="s">
         <v>8</v>
@@ -2460,13 +2575,15 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
-        <v>94893438549</v>
+        <v>375322</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C78" s="1"/>
-      <c r="D78" s="4"/>
+      <c r="D78" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1" t="s">
         <v>8</v>
@@ -2474,14 +2591,14 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
-        <v>375322</v>
+        <v>692565</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1" t="s">
@@ -2490,7 +2607,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
-        <v>692565</v>
+        <v>867039</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>6</v>
@@ -2506,14 +2623,14 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
-        <v>867039</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81" s="1"/>
+        <v>9955937289</v>
+      </c>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D81" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="1" t="s">
@@ -2522,14 +2639,16 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
-        <v>9955937289</v>
-      </c>
-      <c r="B82" s="1"/>
+        <v>15930796998</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C82" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E82" s="1"/>
       <c r="F82" s="1" t="s">
@@ -2538,11 +2657,9 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
-        <v>15930796998</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>15930802980</v>
+      </c>
+      <c r="B83" s="1"/>
       <c r="C83" s="1" t="s">
         <v>6</v>
       </c>
@@ -2556,14 +2673,14 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
-        <v>15930802980</v>
-      </c>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>20603332889</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="1"/>
       <c r="D84" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1" t="s">
@@ -2572,14 +2689,16 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
-        <v>20603332889</v>
+        <v>31828499803</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C85" s="1"/>
+      <c r="C85" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D85" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1" t="s">
@@ -2588,7 +2707,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
-        <v>31828499803</v>
+        <v>75424460291</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>6</v>
@@ -2597,7 +2716,7 @@
         <v>6</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1" t="s">
@@ -2606,16 +2725,14 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
-        <v>75424460291</v>
+        <v>9229</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="C87" s="1"/>
       <c r="D87" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1" t="s">
@@ -2624,15 +2741,13 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
-        <v>9229</v>
+        <v>160202</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C88" s="1"/>
-      <c r="D88" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="D88" s="4"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1" t="s">
         <v>8</v>
@@ -2640,7 +2755,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
-        <v>160202</v>
+        <v>176044</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>6</v>
@@ -2654,13 +2769,15 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
-        <v>176044</v>
+        <v>352381</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C90" s="1"/>
-      <c r="D90" s="4"/>
+      <c r="D90" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="E90" s="1"/>
       <c r="F90" s="1" t="s">
         <v>8</v>
@@ -2668,15 +2785,13 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
-        <v>352381</v>
+        <v>1109570</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C91" s="1"/>
-      <c r="D91" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="D91" s="4"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1" t="s">
         <v>8</v>
@@ -2684,13 +2799,15 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
-        <v>1109570</v>
+        <v>1220330</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C92" s="1"/>
-      <c r="D92" s="4"/>
+      <c r="D92" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1" t="s">
         <v>8</v>
@@ -2698,15 +2815,13 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
-        <v>1220330</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="1"/>
-      <c r="D93" s="4" t="s">
-        <v>10</v>
-      </c>
+        <v>60129750310</v>
+      </c>
+      <c r="B93" s="1"/>
+      <c r="C93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D93" s="4"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1" t="s">
         <v>8</v>
@@ -2714,7 +2829,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
-        <v>60129750310</v>
+        <v>63707777308</v>
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="1" t="s">
@@ -2728,7 +2843,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
-        <v>63707777308</v>
+        <v>94410984349</v>
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="1" t="s">
@@ -2742,13 +2857,15 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
-        <v>94410984349</v>
+        <v>1943263302</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D96" s="4"/>
+      <c r="D96" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="E96" s="1"/>
       <c r="F96" s="1" t="s">
         <v>8</v>
@@ -2756,7 +2873,7 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
-        <v>1943263302</v>
+        <v>3293140335</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1" t="s">
@@ -2772,7 +2889,7 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
-        <v>3293140335</v>
+        <v>11302822365</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1" t="s">
@@ -2788,14 +2905,12 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
-        <v>11302822365</v>
+        <v>4487688957</v>
       </c>
       <c r="B99" s="1"/>
-      <c r="C99" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="C99" s="1"/>
       <c r="D99" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E99" s="1"/>
       <c r="F99" s="1" t="s">
@@ -2804,7 +2919,7 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
-        <v>4487688957</v>
+        <v>49293710153</v>
       </c>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -2818,12 +2933,14 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
-        <v>49293710153</v>
+        <v>62206311615</v>
       </c>
       <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
+      <c r="C101" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D101" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E101" s="1"/>
       <c r="F101" s="1" t="s">
@@ -2832,12 +2949,12 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
-        <v>62206311615</v>
-      </c>
-      <c r="B102" s="1"/>
-      <c r="C102" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>1409107</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="1"/>
       <c r="D102" s="4" t="s">
         <v>10</v>
       </c>
@@ -2848,14 +2965,14 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
-        <v>1409107</v>
+        <v>1455133</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E103" s="1"/>
       <c r="F103" s="1" t="s">
@@ -2864,14 +2981,14 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
-        <v>1455133</v>
+        <v>1524208</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E104" s="1"/>
       <c r="F104" s="1" t="s">
@@ -2880,7 +2997,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
-        <v>1524208</v>
+        <v>5165202</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>6</v>
@@ -2896,15 +3013,13 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
-        <v>5165202</v>
+        <v>6626238</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C106" s="1"/>
-      <c r="D106" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="D106" s="4"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1" t="s">
         <v>8</v>
@@ -2912,13 +3027,17 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
-        <v>6626238</v>
+        <v>1754503586</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C107" s="1"/>
-      <c r="D107" s="4"/>
+      <c r="C107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E107" s="1"/>
       <c r="F107" s="1" t="s">
         <v>8</v>
@@ -2926,16 +3045,14 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
-        <v>1754503586</v>
+        <v>2820058205</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="C108" s="1"/>
       <c r="D108" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E108" s="1"/>
       <c r="F108" s="1" t="s">
@@ -2944,14 +3061,14 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
-        <v>2820058205</v>
+        <v>4099781674</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E109" s="1"/>
       <c r="F109" s="1" t="s">
@@ -2960,14 +3077,14 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
-        <v>4099781674</v>
+        <v>5485659101</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E110" s="1"/>
       <c r="F110" s="1" t="s">
@@ -2976,15 +3093,13 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
-        <v>5485659101</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C111" s="1"/>
-      <c r="D111" s="4" t="s">
-        <v>10</v>
-      </c>
+        <v>10755314468</v>
+      </c>
+      <c r="B111" s="1"/>
+      <c r="C111" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D111" s="4"/>
       <c r="E111" s="1"/>
       <c r="F111" s="1" t="s">
         <v>8</v>
@@ -2992,13 +3107,13 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
-        <v>10755314468</v>
+        <v>1742245404</v>
       </c>
       <c r="B112" s="1"/>
-      <c r="C112" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D112" s="4"/>
+      <c r="C112" s="1"/>
+      <c r="D112" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E112" s="1"/>
       <c r="F112" s="1" t="s">
         <v>8</v>
@@ -3006,12 +3121,16 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
-        <v>1742245404</v>
-      </c>
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
+        <v>1872891071</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D113" s="4" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E113" s="1"/>
       <c r="F113" s="1" t="s">
@@ -3020,17 +3139,13 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
-        <v>1872891071</v>
+        <v>6300019446</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>13</v>
-      </c>
+      <c r="C114" s="1"/>
+      <c r="D114" s="4"/>
       <c r="E114" s="1"/>
       <c r="F114" s="1" t="s">
         <v>8</v>
@@ -3038,7 +3153,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
-        <v>6300019446</v>
+        <v>7297222445</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>6</v>
@@ -3052,13 +3167,13 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
-        <v>7297222445</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>568440935</v>
+      </c>
+      <c r="B116" s="1"/>
       <c r="C116" s="1"/>
-      <c r="D116" s="4"/>
+      <c r="D116" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E116" s="1"/>
       <c r="F116" s="1" t="s">
         <v>8</v>
@@ -3066,13 +3181,13 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
-        <v>568440935</v>
+        <v>5488002944</v>
       </c>
       <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="C117" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D117" s="4"/>
       <c r="E117" s="1"/>
       <c r="F117" s="1" t="s">
         <v>8</v>
@@ -3080,12 +3195,12 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
-        <v>5488002944</v>
-      </c>
-      <c r="B118" s="1"/>
-      <c r="C118" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>1827618</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="1"/>
       <c r="D118" s="4"/>
       <c r="E118" s="1"/>
       <c r="F118" s="1" t="s">
@@ -3094,13 +3209,15 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
-        <v>1827618</v>
+        <v>1834584</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C119" s="1"/>
-      <c r="D119" s="4"/>
+      <c r="D119" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="E119" s="1"/>
       <c r="F119" s="1" t="s">
         <v>8</v>
@@ -3108,15 +3225,13 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
-        <v>1834584</v>
+        <v>17382940802</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C120" s="1"/>
-      <c r="D120" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="D120" s="4"/>
       <c r="E120" s="1"/>
       <c r="F120" s="1" t="s">
         <v>8</v>
@@ -3124,13 +3239,13 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
-        <v>17382940802</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>61707357323</v>
+      </c>
+      <c r="B121" s="1"/>
       <c r="C121" s="1"/>
-      <c r="D121" s="4"/>
+      <c r="D121" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E121" s="1"/>
       <c r="F121" s="1" t="s">
         <v>8</v>
@@ -3138,12 +3253,14 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
-        <v>61707357323</v>
-      </c>
-      <c r="B122" s="1"/>
+        <v>5361133</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C122" s="1"/>
       <c r="D122" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E122" s="1"/>
       <c r="F122" s="1" t="s">
@@ -3152,7 +3269,7 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
-        <v>5361133</v>
+        <v>11194359</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>6</v>
@@ -3168,7 +3285,7 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
-        <v>11194359</v>
+        <v>35324376</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>6</v>
@@ -3184,7 +3301,7 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
-        <v>35324376</v>
+        <v>36184390</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>6</v>
@@ -3200,14 +3317,14 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
-        <v>36184390</v>
+        <v>92359426320</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E126" s="1"/>
       <c r="F126" s="1" t="s">
@@ -3216,7 +3333,7 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
-        <v>92359426320</v>
+        <v>2149575</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>6</v>
@@ -3232,7 +3349,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
-        <v>2149575</v>
+        <v>3382076519</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>6</v>
@@ -3248,12 +3365,12 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
-        <v>3382076519</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C129" s="1"/>
+        <v>56905580520</v>
+      </c>
+      <c r="B129" s="1"/>
+      <c r="C129" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D129" s="4" t="s">
         <v>10</v>
       </c>
@@ -3264,14 +3381,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
-        <v>56905580520</v>
-      </c>
-      <c r="B130" s="1"/>
+        <v>284471313</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C130" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E130" s="1"/>
       <c r="F130" s="1" t="s">
@@ -3280,16 +3399,14 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
-        <v>284471313</v>
+        <v>95044353191</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="C131" s="1"/>
       <c r="D131" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E131" s="1"/>
       <c r="F131" s="1" t="s">
@@ -3298,7 +3415,7 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
-        <v>95044353191</v>
+        <v>87026902172</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>6</v>
@@ -3314,12 +3431,14 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
-        <v>87026902172</v>
+        <v>74802585268</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C133" s="1"/>
+      <c r="C133" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D133" s="4" t="s">
         <v>10</v>
       </c>
@@ -3330,7 +3449,7 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
-        <v>74802585268</v>
+        <v>64074072149</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>6</v>
@@ -3338,9 +3457,7 @@
       <c r="C134" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D134" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="D134" s="4"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1" t="s">
         <v>8</v>
@@ -3348,7 +3465,7 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
-        <v>64074072149</v>
+        <v>3633872345</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>6</v>
@@ -3356,7 +3473,9 @@
       <c r="C135" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D135" s="4"/>
+      <c r="D135" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1" t="s">
         <v>8</v>
@@ -3364,7 +3483,7 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
-        <v>3633872345</v>
+        <v>103076301</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>6</v>
@@ -3373,7 +3492,7 @@
         <v>6</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E136" s="1"/>
       <c r="F136" s="1" t="s">
@@ -3382,7 +3501,7 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
-        <v>103076301</v>
+        <v>1167202635</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>6</v>
@@ -3391,7 +3510,7 @@
         <v>6</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E137" s="1"/>
       <c r="F137" s="1" t="s">
@@ -3400,7 +3519,7 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
-        <v>1167202635</v>
+        <v>56919069504</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>6</v>
@@ -3418,16 +3537,14 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
-        <v>56919069504</v>
+        <v>13080839633</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="C139" s="1"/>
       <c r="D139" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E139" s="1"/>
       <c r="F139" s="1" t="s">
@@ -3436,14 +3553,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
-        <v>13080839633</v>
+        <v>97485632515</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C140" s="1"/>
+      <c r="C140" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D140" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E140" s="1"/>
       <c r="F140" s="1" t="s">
@@ -3452,16 +3571,14 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
-        <v>97485632515</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>11202344410</v>
+      </c>
+      <c r="B141" s="1"/>
       <c r="C141" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E141" s="1"/>
       <c r="F141" s="1" t="s">
@@ -3470,14 +3587,16 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
-        <v>11202344410</v>
-      </c>
-      <c r="B142" s="1"/>
+        <v>7167052302</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C142" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E142" s="1"/>
       <c r="F142" s="1" t="s">
@@ -3486,16 +3605,14 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
-        <v>7167052302</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>6398143604</v>
+      </c>
+      <c r="B143" s="1"/>
       <c r="C143" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E143" s="1"/>
       <c r="F143" s="1" t="s">
@@ -3504,14 +3621,14 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
-        <v>6398143604</v>
+        <v>2331911355</v>
       </c>
       <c r="B144" s="1"/>
       <c r="C144" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E144" s="1"/>
       <c r="F144" s="1" t="s">
@@ -3520,14 +3637,14 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
-        <v>2331911355</v>
+        <v>16874878638</v>
       </c>
       <c r="B145" s="1"/>
       <c r="C145" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E145" s="1"/>
       <c r="F145" s="1" t="s">
@@ -3536,7 +3653,7 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
-        <v>16874878638</v>
+        <v>44367066304</v>
       </c>
       <c r="B146" s="1"/>
       <c r="C146" s="1" t="s">
@@ -3552,7 +3669,7 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
-        <v>44367066304</v>
+        <v>46272803869</v>
       </c>
       <c r="B147" s="1"/>
       <c r="C147" s="1" t="s">
@@ -3568,15 +3685,15 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
-        <v>46272803869</v>
-      </c>
-      <c r="B148" s="1"/>
+        <v>32298315191</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C148" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D148" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="D148" s="4"/>
       <c r="E148" s="1"/>
       <c r="F148" s="1" t="s">
         <v>8</v>
@@ -3584,7 +3701,7 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
-        <v>32298315191</v>
+        <v>8888285601</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>6</v>
@@ -3600,7 +3717,7 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
-        <v>8888285601</v>
+        <v>1615275401</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>6</v>
@@ -3608,7 +3725,9 @@
       <c r="C150" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D150" s="4"/>
+      <c r="D150" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E150" s="1"/>
       <c r="F150" s="1" t="s">
         <v>8</v>
@@ -3616,16 +3735,14 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
-        <v>1615275401</v>
+        <v>6011652760</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="C151" s="1"/>
       <c r="D151" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E151" s="1"/>
       <c r="F151" s="1" t="s">
@@ -3634,14 +3751,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
-        <v>6011652760</v>
+        <v>57908893104</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C152" s="1"/>
+      <c r="C152" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D152" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E152" s="1"/>
       <c r="F152" s="1" t="s">
@@ -3650,16 +3769,14 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
-        <v>57908893104</v>
+        <v>70586931295</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C153" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="C153" s="1"/>
       <c r="D153" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E153" s="1"/>
       <c r="F153" s="1" t="s">
@@ -3668,14 +3785,14 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
-        <v>70586931295</v>
+        <v>97407828253</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C154" s="1"/>
       <c r="D154" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E154" s="1"/>
       <c r="F154" s="1" t="s">
@@ -3684,14 +3801,14 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
-        <v>97407828253</v>
+        <v>3017306607</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C155" s="1"/>
       <c r="D155" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1" t="s">
@@ -3700,14 +3817,14 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
-        <v>3017306607</v>
+        <v>11431230421</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C156" s="1"/>
       <c r="D156" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E156" s="1"/>
       <c r="F156" s="1" t="s">
@@ -3716,15 +3833,15 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
-        <v>11431230421</v>
+        <v>1705491359</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C157" s="1"/>
-      <c r="D157" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="C157" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D157" s="4"/>
       <c r="E157" s="1"/>
       <c r="F157" s="1" t="s">
         <v>8</v>
@@ -3732,7 +3849,7 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
-        <v>1705491359</v>
+        <v>92055613553</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>6</v>
@@ -3740,7 +3857,9 @@
       <c r="C158" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D158" s="4"/>
+      <c r="D158" s="4" t="s">
+        <v>13</v>
+      </c>
       <c r="E158" s="1"/>
       <c r="F158" s="1" t="s">
         <v>8</v>
@@ -3748,7 +3867,7 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
-        <v>92055613553</v>
+        <v>4434895303</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>6</v>
@@ -3757,7 +3876,7 @@
         <v>6</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E159" s="1"/>
       <c r="F159" s="1" t="s">
@@ -3766,7 +3885,7 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
-        <v>4434895303</v>
+        <v>5724205602</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>6</v>
@@ -3774,9 +3893,7 @@
       <c r="C160" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D160" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="D160" s="4"/>
       <c r="E160" s="1"/>
       <c r="F160" s="1" t="s">
         <v>8</v>
@@ -3784,7 +3901,7 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
-        <v>5724205602</v>
+        <v>3670862048</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>6</v>
@@ -3792,7 +3909,9 @@
       <c r="C161" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D161" s="4"/>
+      <c r="D161" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="E161" s="1"/>
       <c r="F161" s="1" t="s">
         <v>8</v>
@@ -3800,7 +3919,7 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
-        <v>3670862048</v>
+        <v>8874532792</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>6</v>
@@ -3809,7 +3928,7 @@
         <v>6</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E162" s="1"/>
       <c r="F162" s="1" t="s">
@@ -3818,7 +3937,7 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
-        <v>8874532792</v>
+        <v>62602713287</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>6</v>
@@ -3827,7 +3946,7 @@
         <v>6</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E163" s="1"/>
       <c r="F163" s="1" t="s">
@@ -3836,11 +3955,9 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
-        <v>62602713287</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>9006781940</v>
+      </c>
+      <c r="B164" s="1"/>
       <c r="C164" s="1" t="s">
         <v>6</v>
       </c>
@@ -3854,14 +3971,12 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
-        <v>9006781940</v>
+        <v>6062529248</v>
       </c>
       <c r="B165" s="1"/>
-      <c r="C165" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="C165" s="1"/>
       <c r="D165" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E165" s="1"/>
       <c r="F165" s="1" t="s">
@@ -3870,12 +3985,14 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
-        <v>6062529248</v>
+        <v>11652859918</v>
       </c>
       <c r="B166" s="1"/>
-      <c r="C166" s="1"/>
+      <c r="C166" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D166" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E166" s="1"/>
       <c r="F166" s="1" t="s">
@@ -3884,7 +4001,7 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
-        <v>11652859918</v>
+        <v>14693733601</v>
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="1" t="s">
@@ -3900,14 +4017,14 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
-        <v>14693733601</v>
+        <v>93842155620</v>
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E168" s="1"/>
       <c r="F168" s="1" t="s">
@@ -3916,15 +4033,15 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
-        <v>93842155620</v>
-      </c>
-      <c r="B169" s="1"/>
+        <v>32762364</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C169" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D169" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="D169" s="4"/>
       <c r="E169" s="1"/>
       <c r="F169" s="1" t="s">
         <v>8</v>
@@ -3932,15 +4049,15 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
-        <v>32762364</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>38628015</v>
+      </c>
+      <c r="B170" s="1"/>
       <c r="C170" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D170" s="4"/>
+      <c r="D170" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E170" s="1"/>
       <c r="F170" s="1" t="s">
         <v>8</v>
@@ -3948,15 +4065,13 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
-        <v>38628015</v>
+        <v>71667377</v>
       </c>
       <c r="B171" s="1"/>
       <c r="C171" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D171" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="D171" s="4"/>
       <c r="E171" s="1"/>
       <c r="F171" s="1" t="s">
         <v>8</v>
@@ -3964,13 +4079,15 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
-        <v>71667377</v>
+        <v>251356</v>
       </c>
       <c r="B172" s="1"/>
       <c r="C172" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D172" s="4"/>
+      <c r="D172" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E172" s="1"/>
       <c r="F172" s="1" t="s">
         <v>8</v>
@@ -3978,15 +4095,15 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
-        <v>251356</v>
-      </c>
-      <c r="B173" s="1"/>
+        <v>995207</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C173" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D173" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="D173" s="4"/>
       <c r="E173" s="1"/>
       <c r="F173" s="1" t="s">
         <v>8</v>
@@ -3994,7 +4111,7 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
-        <v>995207</v>
+        <v>1322338</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>6</v>
@@ -4010,11 +4127,9 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
-        <v>1322338</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>5211913</v>
+      </c>
+      <c r="B175" s="1"/>
       <c r="C175" s="1" t="s">
         <v>6</v>
       </c>
@@ -4026,13 +4141,15 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
-        <v>5211913</v>
-      </c>
-      <c r="B176" s="1"/>
-      <c r="C176" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D176" s="4"/>
+        <v>54783321</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C176" s="1"/>
+      <c r="D176" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="E176" s="1"/>
       <c r="F176" s="1" t="s">
         <v>8</v>
@@ -4040,7 +4157,7 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
-        <v>54783321</v>
+        <v>187948313</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>6</v>
@@ -4056,7 +4173,7 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
-        <v>187948313</v>
+        <v>1175017</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>6</v>
@@ -4072,15 +4189,13 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
-        <v>1175017</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C179" s="1"/>
-      <c r="D179" s="4" t="s">
-        <v>7</v>
-      </c>
+        <v>13693778</v>
+      </c>
+      <c r="B179" s="1"/>
+      <c r="C179" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D179" s="4"/>
       <c r="E179" s="1"/>
       <c r="F179" s="1" t="s">
         <v>8</v>
@@ -4088,13 +4203,15 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
-        <v>13693778</v>
-      </c>
-      <c r="B180" s="1"/>
-      <c r="C180" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D180" s="4"/>
+        <v>19595905</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C180" s="1"/>
+      <c r="D180" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="E180" s="1"/>
       <c r="F180" s="1" t="s">
         <v>8</v>
@@ -4102,14 +4219,14 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
-        <v>19595905</v>
+        <v>72335319</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C181" s="1"/>
       <c r="D181" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E181" s="1"/>
       <c r="F181" s="1" t="s">
@@ -4118,14 +4235,14 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
-        <v>72335319</v>
+        <v>141827343</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C182" s="1"/>
       <c r="D182" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E182" s="1"/>
       <c r="F182" s="1" t="s">
@@ -4134,15 +4251,13 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
-        <v>141827343</v>
+        <v>152671307</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C183" s="1"/>
-      <c r="D183" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="D183" s="4"/>
       <c r="E183" s="1"/>
       <c r="F183" s="1" t="s">
         <v>8</v>
@@ -4150,13 +4265,15 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
-        <v>152671307</v>
+        <v>176295356</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C184" s="1"/>
-      <c r="D184" s="4"/>
+      <c r="D184" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="E184" s="1"/>
       <c r="F184" s="1" t="s">
         <v>8</v>
@@ -4164,15 +4281,13 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
-        <v>176295356</v>
+        <v>188854037</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C185" s="1"/>
-      <c r="D185" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="D185" s="4"/>
       <c r="E185" s="1"/>
       <c r="F185" s="1" t="s">
         <v>8</v>
@@ -4180,7 +4295,7 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" s="2">
-        <v>188854037</v>
+        <v>261974050</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>6</v>
@@ -4194,13 +4309,15 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" s="2">
-        <v>261974050</v>
+        <v>279698003</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C187" s="1"/>
-      <c r="D187" s="4"/>
+      <c r="D187" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E187" s="1"/>
       <c r="F187" s="1" t="s">
         <v>8</v>
@@ -4208,15 +4325,13 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" s="2">
-        <v>279698003</v>
+        <v>313186308</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C188" s="1"/>
-      <c r="D188" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="D188" s="4"/>
       <c r="E188" s="1"/>
       <c r="F188" s="1" t="s">
         <v>8</v>
@@ -4224,7 +4339,7 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" s="2">
-        <v>313186308</v>
+        <v>342804057</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>6</v>
@@ -4238,7 +4353,7 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" s="2">
-        <v>342804057</v>
+        <v>413071006</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>6</v>
@@ -4252,13 +4367,15 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
-        <v>413071006</v>
+        <v>415141222</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C191" s="1"/>
-      <c r="D191" s="4"/>
+      <c r="D191" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E191" s="1"/>
       <c r="F191" s="1" t="s">
         <v>8</v>
@@ -4266,14 +4383,14 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
-        <v>415141222</v>
+        <v>420585540</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C192" s="1"/>
       <c r="D192" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E192" s="1"/>
       <c r="F192" s="1" t="s">
@@ -4282,14 +4399,16 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
-        <v>420585540</v>
+        <v>90200551</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C193" s="1"/>
+      <c r="C193" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D193" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E193" s="1"/>
       <c r="F193" s="1" t="s">
@@ -4298,7 +4417,7 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
-        <v>90200551</v>
+        <v>408855509</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>6</v>
@@ -4307,7 +4426,7 @@
         <v>6</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E194" s="1"/>
       <c r="F194" s="1" t="s">
@@ -4316,7 +4435,7 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
-        <v>408855509</v>
+        <v>3867409501</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>6</v>
@@ -4334,16 +4453,14 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
-        <v>3867409501</v>
-      </c>
-      <c r="B196" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>4449548647</v>
+      </c>
+      <c r="B196" s="1"/>
       <c r="C196" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E196" s="1"/>
       <c r="F196" s="1" t="s">
@@ -4352,14 +4469,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
-        <v>4449548647</v>
-      </c>
-      <c r="B197" s="1"/>
+        <v>4723145486</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C197" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E197" s="1"/>
       <c r="F197" s="1" t="s">
@@ -4368,17 +4487,13 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
-        <v>4723145486</v>
+        <v>149071</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D198" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="C198" s="1"/>
+      <c r="D198" s="4"/>
       <c r="E198" s="1"/>
       <c r="F198" s="1" t="s">
         <v>8</v>
@@ -4386,13 +4501,15 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
-        <v>149071</v>
+        <v>6272320</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C199" s="1"/>
-      <c r="D199" s="4"/>
+      <c r="D199" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E199" s="1"/>
       <c r="F199" s="1" t="s">
         <v>8</v>
@@ -4400,7 +4517,7 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
-        <v>6272320</v>
+        <v>6313531</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>6</v>
@@ -4416,15 +4533,13 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
-        <v>6313531</v>
+        <v>6340342</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C201" s="1"/>
-      <c r="D201" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="D201" s="4"/>
       <c r="E201" s="1"/>
       <c r="F201" s="1" t="s">
         <v>8</v>
@@ -4432,13 +4547,15 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
-        <v>6340342</v>
+        <v>7231342</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C202" s="1"/>
-      <c r="D202" s="4"/>
+      <c r="D202" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="E202" s="1"/>
       <c r="F202" s="1" t="s">
         <v>8</v>
@@ -4446,15 +4563,13 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
-        <v>7231342</v>
+        <v>11528311</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C203" s="1"/>
-      <c r="D203" s="4" t="s">
-        <v>9</v>
-      </c>
+      <c r="D203" s="4"/>
       <c r="E203" s="1"/>
       <c r="F203" s="1" t="s">
         <v>8</v>
@@ -4462,13 +4577,13 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
-        <v>11528311</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>247324</v>
+      </c>
+      <c r="B204" s="1"/>
       <c r="C204" s="1"/>
-      <c r="D204" s="4"/>
+      <c r="D204" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E204" s="1"/>
       <c r="F204" s="1" t="s">
         <v>8</v>
@@ -4476,13 +4591,13 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
-        <v>247324</v>
-      </c>
-      <c r="B205" s="1"/>
+        <v>308307</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C205" s="1"/>
-      <c r="D205" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="D205" s="4"/>
       <c r="E205" s="1"/>
       <c r="F205" s="1" t="s">
         <v>8</v>
@@ -4490,7 +4605,7 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" s="2">
-        <v>308307</v>
+        <v>2822350</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>6</v>
@@ -4504,7 +4619,7 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" s="2">
-        <v>2822350</v>
+        <v>3469344</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>6</v>
@@ -4518,7 +4633,7 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" s="2">
-        <v>3469344</v>
+        <v>4868250</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>6</v>
@@ -4532,12 +4647,12 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" s="2">
-        <v>4868250</v>
-      </c>
-      <c r="B209" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C209" s="1"/>
+        <v>5743095</v>
+      </c>
+      <c r="B209" s="1"/>
+      <c r="C209" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D209" s="4"/>
       <c r="E209" s="1"/>
       <c r="F209" s="1" t="s">
@@ -4546,12 +4661,12 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" s="2">
-        <v>5743095</v>
-      </c>
-      <c r="B210" s="1"/>
-      <c r="C210" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>1450336</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C210" s="1"/>
       <c r="D210" s="4"/>
       <c r="E210" s="1"/>
       <c r="F210" s="1" t="s">
@@ -4560,12 +4675,12 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" s="2">
-        <v>1450336</v>
-      </c>
-      <c r="B211" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C211" s="1"/>
+        <v>1703307</v>
+      </c>
+      <c r="B211" s="1"/>
+      <c r="C211" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D211" s="4"/>
       <c r="E211" s="1"/>
       <c r="F211" s="1" t="s">
@@ -4574,13 +4689,15 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" s="2">
-        <v>1703307</v>
-      </c>
-      <c r="B212" s="1"/>
-      <c r="C212" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D212" s="4"/>
+        <v>2613352</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C212" s="1"/>
+      <c r="D212" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E212" s="1"/>
       <c r="F212" s="1" t="s">
         <v>8</v>
@@ -4588,15 +4705,13 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="2">
-        <v>2613352</v>
+        <v>2621533</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C213" s="1"/>
-      <c r="D213" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="D213" s="4"/>
       <c r="E213" s="1"/>
       <c r="F213" s="1" t="s">
         <v>8</v>
@@ -4604,13 +4719,15 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="2">
-        <v>2621533</v>
+        <v>3708276</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C214" s="1"/>
-      <c r="D214" s="4"/>
+      <c r="D214" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E214" s="1"/>
       <c r="F214" s="1" t="s">
         <v>8</v>
@@ -4618,14 +4735,12 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="2">
-        <v>3708276</v>
-      </c>
-      <c r="B215" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>8201936582</v>
+      </c>
+      <c r="B215" s="1"/>
       <c r="C215" s="1"/>
       <c r="D215" s="4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E215" s="1"/>
       <c r="F215" s="1" t="s">
@@ -4634,12 +4749,14 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="2">
-        <v>8201936582</v>
-      </c>
-      <c r="B216" s="1"/>
+        <v>636304</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C216" s="1"/>
       <c r="D216" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E216" s="1"/>
       <c r="F216" s="1" t="s">
@@ -4648,15 +4765,13 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="2">
-        <v>636304</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C217" s="1"/>
-      <c r="D217" s="4" t="s">
-        <v>7</v>
-      </c>
+        <v>1694200</v>
+      </c>
+      <c r="B217" s="1"/>
+      <c r="C217" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D217" s="4"/>
       <c r="E217" s="1"/>
       <c r="F217" s="1" t="s">
         <v>8</v>
@@ -4664,12 +4779,12 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="2">
-        <v>1694200</v>
-      </c>
-      <c r="B218" s="1"/>
-      <c r="C218" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>4889339</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C218" s="1"/>
       <c r="D218" s="4"/>
       <c r="E218" s="1"/>
       <c r="F218" s="1" t="s">
@@ -4678,7 +4793,7 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" s="2">
-        <v>4889339</v>
+        <v>5079381</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>6</v>
@@ -4692,7 +4807,7 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" s="2">
-        <v>5079381</v>
+        <v>5114390</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>6</v>
@@ -4706,7 +4821,7 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" s="2">
-        <v>5114390</v>
+        <v>5265339</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>6</v>
@@ -4720,12 +4835,12 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A222" s="2">
-        <v>5265339</v>
-      </c>
-      <c r="B222" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C222" s="1"/>
+        <v>11964723</v>
+      </c>
+      <c r="B222" s="1"/>
+      <c r="C222" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D222" s="4"/>
       <c r="E222" s="1"/>
       <c r="F222" s="1" t="s">
@@ -4734,13 +4849,13 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A223" s="2">
-        <v>11964723</v>
+        <v>42848369</v>
       </c>
       <c r="B223" s="1"/>
-      <c r="C223" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D223" s="4"/>
+      <c r="C223" s="1"/>
+      <c r="D223" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E223" s="1"/>
       <c r="F223" s="1" t="s">
         <v>8</v>
@@ -4748,12 +4863,14 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A224" s="2">
-        <v>42848369</v>
+        <v>156788730</v>
       </c>
       <c r="B224" s="1"/>
-      <c r="C224" s="1"/>
+      <c r="C224" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D224" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E224" s="1"/>
       <c r="F224" s="1" t="s">
@@ -4762,14 +4879,12 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
-        <v>156788730</v>
+        <v>221921745</v>
       </c>
       <c r="B225" s="1"/>
-      <c r="C225" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="C225" s="1"/>
       <c r="D225" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E225" s="1"/>
       <c r="F225" s="1" t="s">
@@ -4778,13 +4893,13 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A226" s="2">
-        <v>221921745</v>
-      </c>
-      <c r="B226" s="1"/>
+        <v>247862258</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C226" s="1"/>
-      <c r="D226" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="D226" s="4"/>
       <c r="E226" s="1"/>
       <c r="F226" s="1" t="s">
         <v>8</v>
@@ -4792,13 +4907,13 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A227" s="2">
-        <v>247862258</v>
-      </c>
-      <c r="B227" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>260357588</v>
+      </c>
+      <c r="B227" s="1"/>
       <c r="C227" s="1"/>
-      <c r="D227" s="4"/>
+      <c r="D227" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E227" s="1"/>
       <c r="F227" s="1" t="s">
         <v>8</v>
@@ -4806,7 +4921,7 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A228" s="2">
-        <v>260357588</v>
+        <v>281685770</v>
       </c>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -4820,7 +4935,7 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A229" s="2">
-        <v>281685770</v>
+        <v>303117214</v>
       </c>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -4834,7 +4949,7 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A230" s="2">
-        <v>303117214</v>
+        <v>345513878</v>
       </c>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -4848,7 +4963,7 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A231" s="2">
-        <v>345513878</v>
+        <v>393343766</v>
       </c>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -4862,13 +4977,13 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A232" s="2">
-        <v>393343766</v>
+        <v>404870406</v>
       </c>
       <c r="B232" s="1"/>
-      <c r="C232" s="1"/>
-      <c r="D232" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="C232" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D232" s="4"/>
       <c r="E232" s="1"/>
       <c r="F232" s="1" t="s">
         <v>8</v>
@@ -4876,13 +4991,15 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A233" s="2">
-        <v>404870406</v>
+        <v>415001994</v>
       </c>
       <c r="B233" s="1"/>
       <c r="C233" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D233" s="4"/>
+      <c r="D233" s="4" t="s">
+        <v>10</v>
+      </c>
       <c r="E233" s="1"/>
       <c r="F233" s="1" t="s">
         <v>8</v>
@@ -4890,14 +5007,14 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A234" s="2">
-        <v>415001994</v>
+        <v>417375638</v>
       </c>
       <c r="B234" s="1"/>
       <c r="C234" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E234" s="1"/>
       <c r="F234" s="1" t="s">
@@ -4906,15 +5023,13 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A235" s="2">
-        <v>417375638</v>
+        <v>461926709</v>
       </c>
       <c r="B235" s="1"/>
       <c r="C235" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D235" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="D235" s="4"/>
       <c r="E235" s="1"/>
       <c r="F235" s="1" t="s">
         <v>8</v>
@@ -4922,7 +5037,7 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A236" s="2">
-        <v>461926709</v>
+        <v>505870568</v>
       </c>
       <c r="B236" s="1"/>
       <c r="C236" s="1" t="s">
@@ -4936,12 +5051,12 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A237" s="2">
-        <v>505870568</v>
-      </c>
-      <c r="B237" s="1"/>
-      <c r="C237" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>733487246</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C237" s="1"/>
       <c r="D237" s="4"/>
       <c r="E237" s="1"/>
       <c r="F237" s="1" t="s">
@@ -4950,13 +5065,13 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A238" s="2">
-        <v>733487246</v>
-      </c>
-      <c r="B238" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>866715029</v>
+      </c>
+      <c r="B238" s="1"/>
       <c r="C238" s="1"/>
-      <c r="D238" s="4"/>
+      <c r="D238" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E238" s="1"/>
       <c r="F238" s="1" t="s">
         <v>8</v>
@@ -4964,12 +5079,14 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A239" s="2">
-        <v>866715029</v>
+        <v>876775202</v>
       </c>
       <c r="B239" s="1"/>
-      <c r="C239" s="1"/>
+      <c r="C239" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D239" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E239" s="1"/>
       <c r="F239" s="1" t="s">
@@ -4978,14 +5095,12 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A240" s="2">
-        <v>876775202</v>
+        <v>965936953</v>
       </c>
       <c r="B240" s="1"/>
-      <c r="C240" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="C240" s="1"/>
       <c r="D240" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E240" s="1"/>
       <c r="F240" s="1" t="s">
@@ -4994,12 +5109,14 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A241" s="2">
-        <v>965936953</v>
+        <v>980772796</v>
       </c>
       <c r="B241" s="1"/>
-      <c r="C241" s="1"/>
+      <c r="C241" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D241" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E241" s="1"/>
       <c r="F241" s="1" t="s">
@@ -5008,15 +5125,13 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A242" s="2">
-        <v>980772796</v>
-      </c>
-      <c r="B242" s="1"/>
-      <c r="C242" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D242" s="4" t="s">
-        <v>12</v>
-      </c>
+        <v>998175277</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C242" s="1"/>
+      <c r="D242" s="4"/>
       <c r="E242" s="1"/>
       <c r="F242" s="1" t="s">
         <v>8</v>
@@ -5024,7 +5139,7 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A243" s="2">
-        <v>998175277</v>
+        <v>1104046377</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>6</v>
@@ -5038,12 +5153,12 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A244" s="2">
-        <v>1104046377</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C244" s="1"/>
+        <v>1129136876</v>
+      </c>
+      <c r="B244" s="1"/>
+      <c r="C244" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D244" s="4"/>
       <c r="E244" s="1"/>
       <c r="F244" s="1" t="s">
@@ -5052,7 +5167,7 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A245" s="2">
-        <v>1129136876</v>
+        <v>1215211767</v>
       </c>
       <c r="B245" s="1"/>
       <c r="C245" s="1" t="s">
@@ -5066,13 +5181,15 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A246" s="2">
-        <v>1215211767</v>
+        <v>1270440276</v>
       </c>
       <c r="B246" s="1"/>
       <c r="C246" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D246" s="4"/>
+      <c r="D246" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="E246" s="1"/>
       <c r="F246" s="1" t="s">
         <v>8</v>
@@ -5080,14 +5197,12 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A247" s="2">
-        <v>1270440276</v>
+        <v>1309511101</v>
       </c>
       <c r="B247" s="1"/>
-      <c r="C247" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="C247" s="1"/>
       <c r="D247" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E247" s="1"/>
       <c r="F247" s="1" t="s">
@@ -5096,12 +5211,14 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A248" s="2">
-        <v>1309511101</v>
+        <v>1313908215</v>
       </c>
       <c r="B248" s="1"/>
-      <c r="C248" s="1"/>
+      <c r="C248" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D248" s="4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E248" s="1"/>
       <c r="F248" s="1" t="s">
@@ -5110,14 +5227,14 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A249" s="2">
-        <v>1313908215</v>
-      </c>
-      <c r="B249" s="1"/>
-      <c r="C249" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>1316735214</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C249" s="1"/>
       <c r="D249" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E249" s="1"/>
       <c r="F249" s="1" t="s">
@@ -5126,15 +5243,13 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A250" s="2">
-        <v>1316735214</v>
+        <v>1327218305</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C250" s="1"/>
-      <c r="D250" s="4" t="s">
-        <v>7</v>
-      </c>
+      <c r="D250" s="4"/>
       <c r="E250" s="1"/>
       <c r="F250" s="1" t="s">
         <v>8</v>
@@ -5142,13 +5257,13 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A251" s="2">
-        <v>1327218305</v>
-      </c>
-      <c r="B251" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>1469330792</v>
+      </c>
+      <c r="B251" s="1"/>
       <c r="C251" s="1"/>
-      <c r="D251" s="4"/>
+      <c r="D251" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E251" s="1"/>
       <c r="F251" s="1" t="s">
         <v>8</v>
@@ -5156,12 +5271,14 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A252" s="2">
-        <v>1469330792</v>
+        <v>1520317905</v>
       </c>
       <c r="B252" s="1"/>
-      <c r="C252" s="1"/>
+      <c r="C252" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D252" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E252" s="1"/>
       <c r="F252" s="1" t="s">
@@ -5170,15 +5287,13 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A253" s="2">
-        <v>1520317905</v>
-      </c>
-      <c r="B253" s="1"/>
-      <c r="C253" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D253" s="4" t="s">
-        <v>12</v>
-      </c>
+        <v>1552683257</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C253" s="1"/>
+      <c r="D253" s="4"/>
       <c r="E253" s="1"/>
       <c r="F253" s="1" t="s">
         <v>8</v>
@@ -5186,13 +5301,13 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A254" s="2">
-        <v>1552683257</v>
-      </c>
-      <c r="B254" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>1752772733</v>
+      </c>
+      <c r="B254" s="1"/>
       <c r="C254" s="1"/>
-      <c r="D254" s="4"/>
+      <c r="D254" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E254" s="1"/>
       <c r="F254" s="1" t="s">
         <v>8</v>
@@ -5200,13 +5315,13 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A255" s="2">
-        <v>1752772733</v>
-      </c>
-      <c r="B255" s="1"/>
+        <v>1902803280</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C255" s="1"/>
-      <c r="D255" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="D255" s="4"/>
       <c r="E255" s="1"/>
       <c r="F255" s="1" t="s">
         <v>8</v>
@@ -5214,7 +5329,7 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A256" s="2">
-        <v>1902803280</v>
+        <v>2045280624</v>
       </c>
       <c r="B256" s="1" t="s">
         <v>6</v>
@@ -5228,13 +5343,15 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A257" s="2">
-        <v>2045280624</v>
-      </c>
-      <c r="B257" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C257" s="1"/>
-      <c r="D257" s="4"/>
+        <v>2346482285</v>
+      </c>
+      <c r="B257" s="1"/>
+      <c r="C257" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D257" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="E257" s="1"/>
       <c r="F257" s="1" t="s">
         <v>8</v>
@@ -5242,15 +5359,13 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A258" s="2">
-        <v>2346482285</v>
-      </c>
-      <c r="B258" s="1"/>
-      <c r="C258" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D258" s="4" t="s">
-        <v>12</v>
-      </c>
+        <v>2448337292</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C258" s="1"/>
+      <c r="D258" s="4"/>
       <c r="E258" s="1"/>
       <c r="F258" s="1" t="s">
         <v>8</v>
@@ -5258,12 +5373,12 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A259" s="2">
-        <v>2448337292</v>
-      </c>
-      <c r="B259" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C259" s="1"/>
+        <v>2467922480</v>
+      </c>
+      <c r="B259" s="1"/>
+      <c r="C259" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D259" s="4"/>
       <c r="E259" s="1"/>
       <c r="F259" s="1" t="s">
@@ -5272,13 +5387,13 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A260" s="2">
-        <v>2467922480</v>
+        <v>2564074286</v>
       </c>
       <c r="B260" s="1"/>
-      <c r="C260" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D260" s="4"/>
+      <c r="C260" s="1"/>
+      <c r="D260" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E260" s="1"/>
       <c r="F260" s="1" t="s">
         <v>8</v>
@@ -5286,13 +5401,13 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A261" s="2">
-        <v>2564074286</v>
-      </c>
-      <c r="B261" s="1"/>
+        <v>2668682665</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C261" s="1"/>
-      <c r="D261" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="D261" s="4"/>
       <c r="E261" s="1"/>
       <c r="F261" s="1" t="s">
         <v>8</v>
@@ -5300,13 +5415,13 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A262" s="2">
-        <v>2668682665</v>
-      </c>
-      <c r="B262" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>2705278931</v>
+      </c>
+      <c r="B262" s="1"/>
       <c r="C262" s="1"/>
-      <c r="D262" s="4"/>
+      <c r="D262" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E262" s="1"/>
       <c r="F262" s="1" t="s">
         <v>8</v>
@@ -5314,12 +5429,14 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A263" s="2">
-        <v>2705278931</v>
+        <v>2792829826</v>
       </c>
       <c r="B263" s="1"/>
-      <c r="C263" s="1"/>
+      <c r="C263" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="D263" s="4" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E263" s="1"/>
       <c r="F263" s="1" t="s">
@@ -5328,14 +5445,12 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A264" s="2">
-        <v>2792829826</v>
+        <v>2936656729</v>
       </c>
       <c r="B264" s="1"/>
-      <c r="C264" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="C264" s="1"/>
       <c r="D264" s="4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E264" s="1"/>
       <c r="F264" s="1" t="s">
@@ -5344,13 +5459,13 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A265" s="2">
-        <v>2936656729</v>
-      </c>
-      <c r="B265" s="1"/>
+        <v>3001797150</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C265" s="1"/>
-      <c r="D265" s="4" t="s">
-        <v>6</v>
-      </c>
+      <c r="D265" s="4"/>
       <c r="E265" s="1"/>
       <c r="F265" s="1" t="s">
         <v>8</v>
@@ -5358,29 +5473,15 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A266" s="2">
-        <v>3001797150</v>
-      </c>
-      <c r="B266" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>3162488869</v>
+      </c>
+      <c r="B266" s="1"/>
       <c r="C266" s="1"/>
-      <c r="D266" s="4"/>
+      <c r="D266" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="E266" s="1"/>
       <c r="F266" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A267" s="2">
-        <v>3162488869</v>
-      </c>
-      <c r="B267" s="1"/>
-      <c r="C267" s="1"/>
-      <c r="D267" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E267" s="1"/>
-      <c r="F267" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5398,13 +5499,13 @@
           <x14:formula1>
             <xm:f>CONFIG!$A$2:$A$30</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E267</xm:sqref>
+          <xm:sqref>E2:E266</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B39606B8-BCD1-49FA-9746-463342DEDFD5}">
           <x14:formula1>
             <xm:f>CONFIG!$C$2:$C$3</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F267</xm:sqref>
+          <xm:sqref>F2:F266</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5429,8 +5530,8 @@
       <c r="C1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>50</v>
+      <c r="E1" s="8" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -5440,8 +5541,8 @@
       <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>56</v>
+      <c r="E2" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -5451,79 +5552,79 @@
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>51</v>
+      <c r="E3" s="9" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>52</v>
+      <c r="E4" s="9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="10" t="s">
-        <v>53</v>
+      <c r="E5" s="9" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>54</v>
+      <c r="E6" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>55</v>
+      <c r="E7" s="9" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="10"/>
+      <c r="E8" s="9"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="10"/>
+      <c r="E9" s="9"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="10"/>
+      <c r="E10" s="9"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="E11" s="10"/>
+      <c r="E11" s="9"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="E12" s="10"/>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="E13" s="10"/>
+      <c r="E13" s="9"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="E14" s="10"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="E15" s="10"/>
+      <c r="E15" s="9"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
@@ -5577,17 +5678,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A07569E-5BDC-415E-ABD1-103C61B67D37}">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="144.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="19" customWidth="1"/>
+    <col min="3" max="3" width="211.21875" style="19" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="16" t="s">
         <v>25</v>
       </c>
       <c r="B1" s="7" t="s">
@@ -5600,323 +5701,380 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2">
+    <row r="2" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="24">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="27">
+        <v>2</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="27">
+        <v>3</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="17">
+        <v>4</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D5" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="17">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C6" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="17">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="17">
+        <v>7</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="17">
+        <v>8</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="17">
+        <v>9</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="17">
+        <v>10</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="17">
+        <v>11</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="17">
+        <v>12</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="20" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D13" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="17">
+        <v>13</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="17">
+        <v>14</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="D15" s="17"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="17">
+        <v>15</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D16" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="17">
+        <v>17</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="D18" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="17">
+        <v>18</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="17">
+        <v>18</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="17">
+        <v>20</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="17">
+        <v>21</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="17">
+        <v>22</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D23" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="17">
+        <v>23</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="17">
+        <v>24</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="D25" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>18</v>
-      </c>
-      <c r="B20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" t="s">
-        <v>55</v>
+    </row>
+    <row r="26" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A26" s="17">
+        <v>25</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A27" s="17">
+        <v>26</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="A28" s="17">
+        <v>27</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -5928,7 +6086,7 @@
           <x14:formula1>
             <xm:f>CONFIG!$E$2:$E$15</xm:f>
           </x14:formula1>
-          <xm:sqref>D16:D24 D2:D14</xm:sqref>
+          <xm:sqref>D16:D28 D2:D14</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5949,79 +6107,79 @@
     <col min="6" max="6" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>63</v>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="13">
+      <c r="A2" s="12">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="13">
         <v>46250</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="14">
         <v>23</v>
       </c>
-      <c r="D2" s="15">
+      <c r="D2" s="14">
         <v>0</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="14">
         <v>0</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="14">
         <v>0</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="15">
         <f>C2+D2+E2+F2</f>
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="13"/>
-      <c r="B3" s="14"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="16"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="15"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="13"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="16"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="15"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="16"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F991E8F-2030-400E-9719-FEFA4C61F94C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F47D5C3-2113-4E9C-9FA3-FE04BF9231FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Massa_HML_B31_FLUXO_INTEGRADO" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="69">
   <si>
     <t>CPF</t>
   </si>
@@ -660,7 +660,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
+        <fgColor theme="3" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1448,33 +1448,37 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="A8" s="21">
         <v>3596776490</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
-        <v>8</v>
+      <c r="B8" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
+      <c r="A9" s="21">
         <v>4234381667</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1" t="s">
-        <v>8</v>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -1496,51 +1500,57 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="A11" s="21">
         <v>9293815990</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="4" t="s">
+      <c r="B11" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1" t="s">
-        <v>8</v>
+      <c r="E11" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
+      <c r="A12" s="21">
         <v>14810271153</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="4" t="s">
+      <c r="B12" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="22"/>
+      <c r="D12" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1" t="s">
-        <v>8</v>
+      <c r="E12" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+      <c r="A13" s="21">
         <v>34866868368</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1" t="s">
-        <v>8</v>
+      <c r="B13" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1654,17 +1664,19 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
+      <c r="A21" s="21">
         <v>4024368818</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1" t="s">
-        <v>8</v>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="23"/>
+      <c r="E21" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -1682,19 +1694,21 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="2">
+      <c r="A23" s="21">
         <v>5863603526</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="4" t="s">
+      <c r="B23" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1" t="s">
-        <v>8</v>
+      <c r="E23" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -1912,19 +1926,21 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="2">
+      <c r="A37" s="21">
         <v>3710335</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1" t="s">
-        <v>8</v>
+      <c r="B37" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="22"/>
+      <c r="D37" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -5683,7 +5699,7 @@
   <cols>
     <col min="1" max="1" width="17.44140625" style="19" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.109375" style="19" customWidth="1"/>
-    <col min="3" max="3" width="211.21875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="140" style="19" customWidth="1"/>
     <col min="4" max="4" width="15.44140625" style="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5716,17 +5732,17 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="27">
+      <c r="A3" s="24">
         <v>2</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="27" t="s">
-        <v>40</v>
+      <c r="D3" s="24" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -5744,17 +5760,17 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="17">
+      <c r="A5" s="27">
         <v>4</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="17" t="s">
-        <v>39</v>
+      <c r="D5" s="27" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -6135,10 +6151,10 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="B2" s="13">
-        <v>46250</v>
+        <v>46251</v>
       </c>
       <c r="C2" s="14">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D2" s="14">
         <v>0</v>
@@ -6151,17 +6167,32 @@
       </c>
       <c r="G2" s="15">
         <f>C2+D2+E2+F2</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="12">
+        <v>11</v>
+      </c>
+      <c r="B3" s="13">
+        <v>46252</v>
+      </c>
+      <c r="C3" s="14">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="14"/>
-      <c r="G3" s="15"/>
+      <c r="D3" s="14">
+        <v>2</v>
+      </c>
+      <c r="E3" s="14">
+        <v>0</v>
+      </c>
+      <c r="F3" s="14">
+        <v>2</v>
+      </c>
+      <c r="G3" s="15">
+        <f t="shared" ref="G3:G5" si="0">C3+D3+E3+F3</f>
+        <v>27</v>
+      </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="12"/>
@@ -6170,7 +6201,10 @@
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
       <c r="F4" s="14"/>
-      <c r="G4" s="15"/>
+      <c r="G4" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="12"/>
@@ -6179,7 +6213,10 @@
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
-      <c r="G5" s="15"/>
+      <c r="G5" s="15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F47D5C3-2113-4E9C-9FA3-FE04BF9231FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB6E577-CCE0-4200-A7C4-91F14BC81474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Massa_HML_B31_FLUXO_INTEGRADO" sheetId="3" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="69">
   <si>
     <t>CPF</t>
   </si>
@@ -660,7 +660,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.79998168889431442"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1554,19 +1554,21 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2">
+      <c r="A14" s="21">
         <v>61902037367</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1" t="s">
-        <v>8</v>
+      <c r="B14" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1858,19 +1860,21 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
+      <c r="A33" s="21">
         <v>68136811091</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1" t="s">
-        <v>8</v>
+      <c r="B33" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="23"/>
+      <c r="E33" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1944,19 +1948,21 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="2">
+      <c r="A38" s="21">
         <v>6787240</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1" t="s">
-        <v>8</v>
+      <c r="B38" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="22"/>
+      <c r="D38" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2118,17 +2124,19 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="2">
+      <c r="A49" s="21">
         <v>9427660</v>
       </c>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D49" s="4"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1" t="s">
-        <v>8</v>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="23"/>
+      <c r="E49" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -5731,7 +5739,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="24">
         <v>2</v>
       </c>
@@ -5745,18 +5753,18 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="27">
+    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="24">
         <v>3</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="27" t="s">
-        <v>40</v>
+      <c r="D4" s="24" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -5773,7 +5781,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="17">
         <v>5</v>
       </c>
@@ -5787,32 +5795,32 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="17">
-        <v>6</v>
-      </c>
-      <c r="B7" s="18" t="s">
+    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="27">
+        <v>6</v>
+      </c>
+      <c r="B7" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>39</v>
+      <c r="D7" s="27" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="17">
+      <c r="A8" s="27">
         <v>7</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="17" t="s">
-        <v>39</v>
+      <c r="D8" s="27" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
@@ -5829,7 +5837,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="17">
         <v>9</v>
       </c>
@@ -5843,7 +5851,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="17">
         <v>10</v>
       </c>
@@ -5871,7 +5879,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="17">
         <v>12</v>
       </c>
@@ -5885,7 +5893,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="17">
         <v>13</v>
       </c>
@@ -5925,7 +5933,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="17">
         <v>16</v>
       </c>
@@ -5939,7 +5947,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="17">
         <v>17</v>
       </c>
@@ -5967,7 +5975,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="17">
         <v>18</v>
       </c>
@@ -5981,7 +5989,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="17">
         <v>20</v>
       </c>
@@ -5995,7 +6003,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="17">
         <v>21</v>
       </c>
@@ -6178,10 +6186,10 @@
         <v>46252</v>
       </c>
       <c r="C3" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" s="14">
         <v>0</v>

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EB6E577-CCE0-4200-A7C4-91F14BC81474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D000EB9-43AF-4D34-99BB-E5B34C72F241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Massa_HML_B31_FLUXO_INTEGRADO" sheetId="3" r:id="rId1"/>
@@ -6186,7 +6186,7 @@
         <v>46252</v>
       </c>
       <c r="C3" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="14">
         <v>3</v>
@@ -6195,7 +6195,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3" s="15">
         <f t="shared" ref="G3:G5" si="0">C3+D3+E3+F3</f>

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D000EB9-43AF-4D34-99BB-E5B34C72F241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502A9BB2-EB40-4197-9B4D-11E8289F9789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Massa_HML_B31_FLUXO_INTEGRADO" sheetId="3" r:id="rId1"/>
@@ -5782,17 +5782,17 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="17">
+      <c r="A6" s="27">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>39</v>
+      <c r="D6" s="27" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502A9BB2-EB40-4197-9B4D-11E8289F9789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E81170-E74C-44B9-981E-B1070E843110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="70">
   <si>
     <t>CPF</t>
   </si>
@@ -294,6 +294,9 @@
 Catálogo: Exige autodeclaração = ATIVADO
 Parâmetro:  144 - Fluxo ATESTMED = LIGADO</t>
     </r>
+  </si>
+  <si>
+    <t>Quantidade de Homologadores</t>
   </si>
 </sst>
 </file>
@@ -454,7 +457,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -664,8 +667,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -836,6 +845,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -881,7 +901,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -948,6 +968,20 @@
     <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1346,19 +1380,21 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="21">
         <v>99418274353</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
+      <c r="E2" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1572,81 +1608,91 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="A15" s="21">
         <v>73620963649</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="4" t="s">
+      <c r="B15" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1" t="s">
-        <v>8</v>
+      <c r="E15" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2">
+      <c r="A16" s="21">
         <v>94332096991</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="4" t="s">
+      <c r="B16" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="22"/>
+      <c r="D16" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1" t="s">
-        <v>8</v>
+      <c r="E16" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+      <c r="A17" s="21">
         <v>99894300391</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="4" t="s">
+      <c r="B17" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1" t="s">
-        <v>8</v>
+      <c r="E17" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2">
+      <c r="A18" s="21">
         <v>737185309</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="4" t="s">
+      <c r="B18" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1" t="s">
+      <c r="E18" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="22" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
+      <c r="A19" s="21">
         <v>1304390373</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1" t="s">
-        <v>8</v>
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1682,17 +1728,19 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+      <c r="A22" s="21">
         <v>5136194960</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1" t="s">
-        <v>8</v>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -5702,16 +5750,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A07569E-5BDC-415E-ABD1-103C61B67D37}">
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.44140625" style="19" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.109375" style="19" customWidth="1"/>
-    <col min="3" max="3" width="140" style="19" customWidth="1"/>
+    <col min="3" max="3" width="81.77734375" style="19" customWidth="1"/>
     <col min="4" max="4" width="15.44140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>25</v>
       </c>
@@ -5724,8 +5773,11 @@
       <c r="D1" s="7" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E1" s="30" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="24">
         <v>1</v>
       </c>
@@ -5738,8 +5790,11 @@
       <c r="D2" s="24" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E2" s="35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="24">
         <v>2</v>
       </c>
@@ -5752,8 +5807,11 @@
       <c r="D3" s="24" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E3" s="35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="24">
         <v>3</v>
       </c>
@@ -5766,8 +5824,11 @@
       <c r="D4" s="24" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E4" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="27">
         <v>4</v>
       </c>
@@ -5780,8 +5841,11 @@
       <c r="D5" s="27" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E5" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="27">
         <v>5</v>
       </c>
@@ -5794,8 +5858,11 @@
       <c r="D6" s="27" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E6" s="34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="27">
         <v>6</v>
       </c>
@@ -5808,8 +5875,11 @@
       <c r="D7" s="27" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E7" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="27">
         <v>7</v>
       </c>
@@ -5822,64 +5892,79 @@
       <c r="D8" s="27" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="17">
-        <v>8</v>
-      </c>
-      <c r="B9" s="18" t="s">
+      <c r="E8" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="31">
+        <v>8</v>
+      </c>
+      <c r="B9" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="17">
+      <c r="D9" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="31">
         <v>9</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="33" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" s="17">
+      <c r="D10" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A11" s="31">
         <v>10</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="33" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
+      <c r="D11" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="31">
         <v>11</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="D12" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A13" s="17">
         <v>12</v>
       </c>
@@ -5892,8 +5977,9 @@
       <c r="D13" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E13" s="9"/>
+    </row>
+    <row r="14" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="17">
         <v>13</v>
       </c>
@@ -5906,8 +5992,9 @@
       <c r="D14" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E14" s="9"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="17">
         <v>14</v>
       </c>
@@ -5918,78 +6005,94 @@
         <v>30</v>
       </c>
       <c r="D15" s="17"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="17">
+      <c r="E15" s="9"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="31">
         <v>15</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="17">
+      <c r="D16" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E16" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="31">
         <v>16</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="17">
+      <c r="D17" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E17" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="31">
         <v>17</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="C18" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="17">
+      <c r="D18" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="31">
         <v>18</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="17">
+      <c r="D19" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E19" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="31">
         <v>18</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="D20" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="17">
         <v>20</v>
       </c>
@@ -6002,36 +6105,43 @@
       <c r="D21" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="17">
+      <c r="E21" s="9"/>
+    </row>
+    <row r="22" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="31">
         <v>21</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="17">
+      <c r="D22" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E22" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="31">
         <v>22</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="D23" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E23" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="17">
         <v>23</v>
       </c>
@@ -6044,8 +6154,9 @@
       <c r="D24" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="E24" s="9"/>
+    </row>
+    <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="17">
         <v>24</v>
       </c>
@@ -6058,22 +6169,26 @@
       <c r="D25" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="72" x14ac:dyDescent="0.3">
-      <c r="A26" s="17">
+      <c r="E25" s="9"/>
+    </row>
+    <row r="26" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A26" s="31">
         <v>25</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="D26" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="D26" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A27" s="17">
         <v>26</v>
       </c>
@@ -6086,8 +6201,9 @@
       <c r="D27" s="17" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="72" x14ac:dyDescent="0.3">
+      <c r="E27" s="9"/>
+    </row>
+    <row r="28" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A28" s="17">
         <v>27</v>
       </c>
@@ -6100,6 +6216,7 @@
       <c r="D28" s="17" t="s">
         <v>39</v>
       </c>
+      <c r="E28" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71E81170-E74C-44B9-981E-B1070E843110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BAF28B1-D7E6-48D0-99EA-4793879944CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Massa_HML_B31_FLUXO_INTEGRADO" sheetId="3" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="CENARIOS" sheetId="5" r:id="rId3"/>
     <sheet name="ResumoDiario" sheetId="6" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CENARIOS!$D$1:$D$28</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="70">
   <si>
     <t>CPF</t>
   </si>
@@ -1696,19 +1699,21 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
+      <c r="A20" s="21">
         <v>2185404938</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="4" t="s">
+      <c r="B20" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="22"/>
+      <c r="D20" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1" t="s">
-        <v>8</v>
+      <c r="E20" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -1762,51 +1767,57 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
+      <c r="A24" s="21">
         <v>12401303685</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="4" t="s">
+      <c r="B24" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="22"/>
+      <c r="D24" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1" t="s">
-        <v>8</v>
+      <c r="E24" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
+      <c r="A25" s="21">
         <v>44771380597</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="4" t="s">
+      <c r="B25" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="22"/>
+      <c r="D25" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1" t="s">
-        <v>8</v>
+      <c r="E25" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="2">
+      <c r="A26" s="21">
         <v>3179868996</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="B26" s="22"/>
+      <c r="C26" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1" t="s">
-        <v>8</v>
+      <c r="E26" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -5210,16 +5221,18 @@
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A243" s="2">
+      <c r="A243" s="21">
         <v>1104046377</v>
       </c>
-      <c r="B243" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C243" s="1"/>
-      <c r="D243" s="4"/>
-      <c r="E243" s="1"/>
-      <c r="F243" s="1" t="s">
+      <c r="B243" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C243" s="22"/>
+      <c r="D243" s="23"/>
+      <c r="E243" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F243" s="22" t="s">
         <v>8</v>
       </c>
     </row>
@@ -5314,17 +5327,19 @@
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A250" s="2">
+      <c r="A250" s="21">
         <v>1327218305</v>
       </c>
-      <c r="B250" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C250" s="1"/>
-      <c r="D250" s="4"/>
-      <c r="E250" s="1"/>
-      <c r="F250" s="1" t="s">
-        <v>8</v>
+      <c r="B250" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C250" s="22"/>
+      <c r="D250" s="23"/>
+      <c r="E250" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F250" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
@@ -5342,33 +5357,37 @@
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A252" s="2">
+      <c r="A252" s="21">
         <v>1520317905</v>
       </c>
-      <c r="B252" s="1"/>
-      <c r="C252" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D252" s="4" t="s">
+      <c r="B252" s="22"/>
+      <c r="C252" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="D252" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="E252" s="1"/>
-      <c r="F252" s="1" t="s">
-        <v>8</v>
+      <c r="E252" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F252" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A253" s="2">
+      <c r="A253" s="21">
         <v>1552683257</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C253" s="1"/>
-      <c r="D253" s="4"/>
-      <c r="E253" s="1"/>
-      <c r="F253" s="1" t="s">
-        <v>8</v>
+      <c r="B253" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C253" s="22"/>
+      <c r="D253" s="23"/>
+      <c r="E253" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F253" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
@@ -5386,31 +5405,35 @@
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A255" s="2">
+      <c r="A255" s="21">
         <v>1902803280</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C255" s="1"/>
-      <c r="D255" s="4"/>
-      <c r="E255" s="1"/>
-      <c r="F255" s="1" t="s">
-        <v>8</v>
+      <c r="B255" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C255" s="22"/>
+      <c r="D255" s="23"/>
+      <c r="E255" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F255" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A256" s="2">
+      <c r="A256" s="21">
         <v>2045280624</v>
       </c>
-      <c r="B256" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C256" s="1"/>
-      <c r="D256" s="4"/>
-      <c r="E256" s="1"/>
-      <c r="F256" s="1" t="s">
-        <v>8</v>
+      <c r="B256" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C256" s="22"/>
+      <c r="D256" s="23"/>
+      <c r="E256" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F256" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
@@ -5430,17 +5453,19 @@
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A258" s="2">
+      <c r="A258" s="21">
         <v>2448337292</v>
       </c>
-      <c r="B258" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C258" s="1"/>
-      <c r="D258" s="4"/>
-      <c r="E258" s="1"/>
-      <c r="F258" s="1" t="s">
-        <v>8</v>
+      <c r="B258" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C258" s="22"/>
+      <c r="D258" s="23"/>
+      <c r="E258" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F258" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
@@ -5472,17 +5497,19 @@
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A261" s="2">
+      <c r="A261" s="21">
         <v>2668682665</v>
       </c>
-      <c r="B261" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C261" s="1"/>
-      <c r="D261" s="4"/>
-      <c r="E261" s="1"/>
-      <c r="F261" s="1" t="s">
-        <v>8</v>
+      <c r="B261" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C261" s="22"/>
+      <c r="D261" s="23"/>
+      <c r="E261" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F261" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
@@ -5530,31 +5557,35 @@
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A265" s="2">
+      <c r="A265" s="21">
         <v>3001797150</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C265" s="1"/>
-      <c r="D265" s="4"/>
-      <c r="E265" s="1"/>
-      <c r="F265" s="1" t="s">
-        <v>8</v>
+      <c r="B265" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C265" s="22"/>
+      <c r="D265" s="23"/>
+      <c r="E265" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F265" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A266" s="2">
+      <c r="A266" s="21">
         <v>3162488869</v>
       </c>
-      <c r="B266" s="1"/>
-      <c r="C266" s="1"/>
-      <c r="D266" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E266" s="1"/>
-      <c r="F266" s="1" t="s">
-        <v>8</v>
+      <c r="B266" s="22"/>
+      <c r="C266" s="22"/>
+      <c r="D266" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E266" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F266" s="22" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5750,6 +5781,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A07569E-5BDC-415E-ABD1-103C61B67D37}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5777,7 +5809,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="24">
         <v>1</v>
       </c>
@@ -5794,7 +5826,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="24">
         <v>2</v>
       </c>
@@ -5811,7 +5843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="24">
         <v>3</v>
       </c>
@@ -5828,41 +5860,41 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="27">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="24">
         <v>4</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="E5" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="27">
+      <c r="D5" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="24">
         <v>5</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D6" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="27">
         <v>6</v>
       </c>
@@ -5876,10 +5908,10 @@
         <v>40</v>
       </c>
       <c r="E7" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="27">
         <v>7</v>
       </c>
@@ -5893,10 +5925,10 @@
         <v>40</v>
       </c>
       <c r="E8" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="31">
         <v>8</v>
       </c>
@@ -5913,7 +5945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="31">
         <v>9</v>
       </c>
@@ -5930,7 +5962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="31">
         <v>10</v>
       </c>
@@ -5947,7 +5979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="31">
         <v>11</v>
       </c>
@@ -6004,10 +6036,12 @@
       <c r="C15" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="17"/>
+      <c r="D15" s="17" t="s">
+        <v>39</v>
+      </c>
       <c r="E15" s="9"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="31">
         <v>15</v>
       </c>
@@ -6024,7 +6058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="31">
         <v>16</v>
       </c>
@@ -6041,7 +6075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="31">
         <v>17</v>
       </c>
@@ -6058,7 +6092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="31">
         <v>18</v>
       </c>
@@ -6075,7 +6109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="31">
         <v>18</v>
       </c>
@@ -6107,7 +6141,7 @@
       </c>
       <c r="E21" s="9"/>
     </row>
-    <row r="22" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="31">
         <v>21</v>
       </c>
@@ -6124,7 +6158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="31">
         <v>22</v>
       </c>
@@ -6171,7 +6205,7 @@
       </c>
       <c r="E25" s="9"/>
     </row>
-    <row r="26" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="31">
         <v>25</v>
       </c>
@@ -6188,37 +6222,48 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A27" s="17">
+    <row r="27" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="31">
         <v>26</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="9"/>
-    </row>
-    <row r="28" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A28" s="17">
+      <c r="D27" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E27" s="34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="31">
         <v>27</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="D28" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="9"/>
+      <c r="D28" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E28" s="34">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="D1:D28" xr:uid="{9A07569E-5BDC-415E-ABD1-103C61B67D37}">
+    <filterColumn colId="0">
+      <filters blank="1">
+        <filter val="NÃO EXECUTADO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -6303,16 +6348,16 @@
         <v>46252</v>
       </c>
       <c r="C3" s="14">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="D3" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E3" s="14">
         <v>0</v>
       </c>
       <c r="F3" s="14">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G3" s="15">
         <f t="shared" ref="G3:G5" si="0">C3+D3+E3+F3</f>

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BAF28B1-D7E6-48D0-99EA-4793879944CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740CBD6E-48FA-47B0-A4A9-9573F5272250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
@@ -42,12 +42,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="70">
   <si>
     <t>CPF</t>
-  </si>
-  <si>
-    <t>Possi período validado</t>
   </si>
   <si>
     <t>Possio período Invalidado</t>
@@ -300,6 +297,9 @@
   </si>
   <si>
     <t>Quantidade de Homologadores</t>
+  </si>
+  <si>
+    <t>Possui período validado</t>
   </si>
 </sst>
 </file>
@@ -666,13 +666,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -904,7 +904,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -938,17 +938,8 @@
     <xf numFmtId="0" fontId="16" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="35" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
@@ -962,6 +953,9 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -971,9 +965,21 @@
     <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -984,7 +990,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1367,509 +1372,517 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="21">
+      <c r="A2" s="18">
         <v>99418274353</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="18">
+        <v>848157362</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="18">
+        <v>20673310</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="19"/>
+      <c r="D4" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F4" s="19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="18">
+        <v>21376310</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="19"/>
+      <c r="D5" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="18">
+        <v>40322335</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="D6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="18">
+        <v>2734924625</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="19"/>
+      <c r="D7" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="18">
+        <v>3596776490</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="18">
+        <v>4234381667</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="20"/>
+      <c r="E9" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="18">
+        <v>9220661837</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="18">
+        <v>9293815990</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="18">
+        <v>14810271153</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="18">
+        <v>34866868368</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="18">
+        <v>61902037367</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="18">
+        <v>73620963649</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="18">
+        <v>94332096991</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="18">
+        <v>99894300391</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="18">
+        <v>737185309</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" s="20" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="21">
-        <v>848157362</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="23" t="s">
+      <c r="E18" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="18">
+        <v>1304390373</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="18">
+        <v>2185404938</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="22" t="s">
+      <c r="E20" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="18">
+        <v>4024368818</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="20"/>
+      <c r="E21" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="18">
+        <v>5136194960</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="18">
+        <v>5863603526</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" s="20" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="21">
-        <v>20673310</v>
-      </c>
-      <c r="B4" s="22" t="s">
+      <c r="E23" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="18">
+        <v>12401303685</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="23" t="s">
+      <c r="E24" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="18">
+        <v>44771380597</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="18">
+        <v>3179868996</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="22" t="s">
+      <c r="E26" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="18">
+        <v>8707937563</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>21376310</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="4" t="s">
+      <c r="E27" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="18">
+        <v>10062959417</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="18">
+        <v>15477671467</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="21">
-        <v>40322335</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="21">
-        <v>2734924625</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="21">
-        <v>3596776490</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="21">
-        <v>4234381667</v>
-      </c>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="21">
-        <v>9220661837</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="21">
-        <v>9293815990</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="21">
-        <v>14810271153</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="21">
-        <v>34866868368</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="21">
-        <v>61902037367</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="21">
-        <v>73620963649</v>
-      </c>
-      <c r="B15" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F15" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="21">
-        <v>94332096991</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="21">
-        <v>99894300391</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="21">
-        <v>737185309</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E18" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="21">
-        <v>1304390373</v>
-      </c>
-      <c r="B19" s="22"/>
-      <c r="C19" s="22"/>
-      <c r="D19" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="21">
-        <v>2185404938</v>
-      </c>
-      <c r="B20" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="22"/>
-      <c r="D20" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="21">
-        <v>4024368818</v>
-      </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="23"/>
-      <c r="E21" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="21">
-        <v>5136194960</v>
-      </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F22" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="21">
-        <v>5863603526</v>
-      </c>
-      <c r="B23" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="22"/>
-      <c r="D23" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="21">
-        <v>12401303685</v>
-      </c>
-      <c r="B24" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="22"/>
-      <c r="D24" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="21">
-        <v>44771380597</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F25" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="21">
-        <v>3179868996</v>
-      </c>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D26" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="2">
-        <v>8707937563</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="2">
-        <v>10062959417</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="2">
-        <v>15477671467</v>
-      </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1" t="s">
-        <v>8</v>
+      <c r="E29" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1878,14 +1891,14 @@
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -1894,82 +1907,88 @@
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="18">
+        <v>33629307000</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="20"/>
+      <c r="E32" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="18">
+        <v>68136811091</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="20"/>
+      <c r="E33" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="18">
+        <v>83002812153</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="2">
-        <v>33629307000</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="21">
-        <v>68136811091</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D33" s="23"/>
-      <c r="E33" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="2">
-        <v>83002812153</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1" t="s">
-        <v>8</v>
+      <c r="E34" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="2">
+      <c r="A35" s="18">
         <v>85179817315</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1" t="s">
-        <v>8</v>
+      <c r="B35" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1978,50 +1997,50 @@
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="21">
+      <c r="A37" s="18">
         <v>3710335</v>
       </c>
-      <c r="B37" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="22"/>
-      <c r="D37" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E37" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F37" s="22" t="s">
-        <v>6</v>
+      <c r="B37" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E37" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="21">
+      <c r="A38" s="18">
         <v>6787240</v>
       </c>
-      <c r="B38" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="22"/>
-      <c r="D38" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F38" s="22" t="s">
-        <v>6</v>
+      <c r="B38" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2029,15 +2048,15 @@
         <v>9366261</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2045,15 +2064,15 @@
         <v>1548301</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E40" s="1"/>
       <c r="F40" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2061,15 +2080,15 @@
         <v>1818384</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2077,15 +2096,15 @@
         <v>59054271</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2093,15 +2112,15 @@
         <v>65913299</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2109,15 +2128,15 @@
         <v>79277209</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E44" s="1"/>
       <c r="F44" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2127,11 +2146,11 @@
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
       <c r="D45" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2141,11 +2160,11 @@
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
       <c r="D46" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E46" s="1"/>
       <c r="F46" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2153,15 +2172,15 @@
         <v>114745218</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E47" s="1"/>
       <c r="F47" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2169,33 +2188,33 @@
         <v>7227906</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="21">
+      <c r="A49" s="18">
         <v>9427660</v>
       </c>
-      <c r="B49" s="22"/>
-      <c r="C49" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D49" s="23"/>
-      <c r="E49" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F49" s="22" t="s">
-        <v>6</v>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="20"/>
+      <c r="E49" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2203,17 +2222,17 @@
         <v>10152148</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E50" s="1"/>
       <c r="F50" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -2221,17 +2240,17 @@
         <v>61461121</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2239,15 +2258,15 @@
         <v>93573006</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2255,15 +2274,15 @@
         <v>95026100</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2271,17 +2290,17 @@
         <v>7494173404</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2289,17 +2308,17 @@
         <v>7496954390</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2307,31 +2326,33 @@
         <v>7502772383</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="2">
+      <c r="A57" s="18">
         <v>234346</v>
       </c>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1" t="s">
-        <v>8</v>
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -2339,15 +2360,15 @@
         <v>251275</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E58" s="1"/>
       <c r="F58" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -2355,15 +2376,15 @@
         <v>40999408</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -2373,11 +2394,11 @@
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
       <c r="D60" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -2385,15 +2406,15 @@
         <v>96619309</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E61" s="1"/>
       <c r="F61" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -2401,13 +2422,13 @@
         <v>2184685550</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="4"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2415,17 +2436,17 @@
         <v>136679390</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E63" s="1"/>
       <c r="F63" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -2433,15 +2454,15 @@
         <v>284905330</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -2449,17 +2470,17 @@
         <v>404822606</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -2467,17 +2488,17 @@
         <v>455785163</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -2486,14 +2507,14 @@
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -2501,13 +2522,13 @@
         <v>98983768304</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="4"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -2515,15 +2536,15 @@
         <v>99052210349</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E69" s="1"/>
       <c r="F69" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
@@ -2533,11 +2554,11 @@
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
@@ -2545,65 +2566,71 @@
         <v>99447444504</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="18">
+        <v>541253913</v>
+      </c>
+      <c r="B72" s="19"/>
+      <c r="C72" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="20"/>
+      <c r="E72" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F72" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="18">
+        <v>583695540</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="18">
+        <v>887361307</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="20" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="2">
-        <v>541253913</v>
-      </c>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D72" s="4"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="2">
-        <v>583695540</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="2">
-        <v>887361307</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1" t="s">
-        <v>8</v>
+      <c r="E74" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F74" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -2611,17 +2638,17 @@
         <v>979170796</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E75" s="1"/>
       <c r="F75" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -2629,17 +2656,17 @@
         <v>1017978506</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E76" s="1"/>
       <c r="F76" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -2647,13 +2674,13 @@
         <v>94893438549</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="4"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -2661,15 +2688,15 @@
         <v>375322</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -2677,15 +2704,15 @@
         <v>692565</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E79" s="1"/>
       <c r="F79" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -2693,15 +2720,15 @@
         <v>867039</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -2710,14 +2737,14 @@
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E81" s="1"/>
       <c r="F81" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -2725,17 +2752,17 @@
         <v>15930796998</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E82" s="1"/>
       <c r="F82" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -2744,14 +2771,14 @@
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E83" s="1"/>
       <c r="F83" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -2759,15 +2786,15 @@
         <v>20603332889</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -2775,17 +2802,17 @@
         <v>31828499803</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -2793,17 +2820,17 @@
         <v>75424460291</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -2811,15 +2838,15 @@
         <v>9229</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -2827,13 +2854,13 @@
         <v>160202</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="4"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -2841,13 +2868,13 @@
         <v>176044</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="4"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -2855,15 +2882,15 @@
         <v>352381</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E90" s="1"/>
       <c r="F90" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -2871,13 +2898,13 @@
         <v>1109570</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="4"/>
       <c r="E91" s="1"/>
       <c r="F91" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -2885,15 +2912,15 @@
         <v>1220330</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -2902,12 +2929,12 @@
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="1"/>
       <c r="F93" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -2916,12 +2943,12 @@
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="1"/>
       <c r="F94" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -2930,12 +2957,12 @@
       </c>
       <c r="B95" s="1"/>
       <c r="C95" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -2944,14 +2971,14 @@
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E96" s="1"/>
       <c r="F96" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -2960,14 +2987,14 @@
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -2976,28 +3003,30 @@
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E98" s="1"/>
       <c r="F98" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="2">
+      <c r="A99" s="18">
         <v>4487688957</v>
       </c>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1" t="s">
-        <v>8</v>
+      <c r="B99" s="19"/>
+      <c r="C99" s="19"/>
+      <c r="D99" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E99" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F99" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
@@ -3007,11 +3036,11 @@
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
       <c r="D100" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E100" s="1"/>
       <c r="F100" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
@@ -3020,14 +3049,14 @@
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E101" s="1"/>
       <c r="F101" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
@@ -3035,15 +3064,15 @@
         <v>1409107</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C102" s="1"/>
       <c r="D102" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E102" s="1"/>
       <c r="F102" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
@@ -3051,15 +3080,15 @@
         <v>1455133</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E103" s="1"/>
       <c r="F103" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
@@ -3067,15 +3096,15 @@
         <v>1524208</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C104" s="1"/>
       <c r="D104" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E104" s="1"/>
       <c r="F104" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
@@ -3083,15 +3112,15 @@
         <v>5165202</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C105" s="1"/>
       <c r="D105" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E105" s="1"/>
       <c r="F105" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
@@ -3099,13 +3128,13 @@
         <v>6626238</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C106" s="1"/>
       <c r="D106" s="4"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -3113,17 +3142,17 @@
         <v>1754503586</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E107" s="1"/>
       <c r="F107" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
@@ -3131,15 +3160,15 @@
         <v>2820058205</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C108" s="1"/>
       <c r="D108" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E108" s="1"/>
       <c r="F108" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
@@ -3147,15 +3176,15 @@
         <v>4099781674</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E109" s="1"/>
       <c r="F109" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
@@ -3163,43 +3192,47 @@
         <v>5485659101</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E110" s="1"/>
       <c r="F110" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="2">
+      <c r="A111" s="18">
         <v>10755314468</v>
       </c>
-      <c r="B111" s="1"/>
-      <c r="C111" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D111" s="4"/>
-      <c r="E111" s="1"/>
-      <c r="F111" s="1" t="s">
-        <v>8</v>
+      <c r="B111" s="19"/>
+      <c r="C111" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D111" s="20"/>
+      <c r="E111" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F111" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="2">
+      <c r="A112" s="18">
         <v>1742245404</v>
       </c>
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E112" s="1"/>
-      <c r="F112" s="1" t="s">
-        <v>8</v>
+      <c r="B112" s="19"/>
+      <c r="C112" s="19"/>
+      <c r="D112" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E112" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F112" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -3207,17 +3240,17 @@
         <v>1872891071</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E113" s="1"/>
       <c r="F113" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -3225,13 +3258,13 @@
         <v>6300019446</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="4"/>
       <c r="E114" s="1"/>
       <c r="F114" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
@@ -3239,41 +3272,45 @@
         <v>7297222445</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C115" s="1"/>
       <c r="D115" s="4"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="2">
+      <c r="A116" s="18">
         <v>568440935</v>
       </c>
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1" t="s">
-        <v>8</v>
+      <c r="B116" s="19"/>
+      <c r="C116" s="19"/>
+      <c r="D116" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E116" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F116" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="2">
+      <c r="A117" s="18">
         <v>5488002944</v>
       </c>
-      <c r="B117" s="1"/>
-      <c r="C117" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D117" s="4"/>
-      <c r="E117" s="1"/>
-      <c r="F117" s="1" t="s">
-        <v>8</v>
+      <c r="B117" s="19"/>
+      <c r="C117" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D117" s="20"/>
+      <c r="E117" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F117" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -3281,13 +3318,13 @@
         <v>1827618</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="4"/>
       <c r="E118" s="1"/>
       <c r="F118" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
@@ -3295,15 +3332,15 @@
         <v>1834584</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E119" s="1"/>
       <c r="F119" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -3311,13 +3348,13 @@
         <v>17382940802</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="4"/>
       <c r="E120" s="1"/>
       <c r="F120" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -3327,11 +3364,11 @@
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="D121" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E121" s="1"/>
       <c r="F121" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
@@ -3339,15 +3376,15 @@
         <v>5361133</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C122" s="1"/>
       <c r="D122" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E122" s="1"/>
       <c r="F122" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
@@ -3355,15 +3392,15 @@
         <v>11194359</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C123" s="1"/>
       <c r="D123" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E123" s="1"/>
       <c r="F123" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
@@ -3371,15 +3408,15 @@
         <v>35324376</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C124" s="1"/>
       <c r="D124" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E124" s="1"/>
       <c r="F124" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
@@ -3387,15 +3424,15 @@
         <v>36184390</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C125" s="1"/>
       <c r="D125" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E125" s="1"/>
       <c r="F125" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -3403,15 +3440,15 @@
         <v>92359426320</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C126" s="1"/>
       <c r="D126" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E126" s="1"/>
       <c r="F126" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
@@ -3419,15 +3456,15 @@
         <v>2149575</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C127" s="1"/>
       <c r="D127" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E127" s="1"/>
       <c r="F127" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
@@ -3435,15 +3472,15 @@
         <v>3382076519</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C128" s="1"/>
       <c r="D128" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
@@ -3452,14 +3489,14 @@
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
@@ -3467,17 +3504,17 @@
         <v>284471313</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E130" s="1"/>
       <c r="F130" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
@@ -3485,15 +3522,15 @@
         <v>95044353191</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C131" s="1"/>
       <c r="D131" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E131" s="1"/>
       <c r="F131" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
@@ -3501,15 +3538,15 @@
         <v>87026902172</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C132" s="1"/>
       <c r="D132" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E132" s="1"/>
       <c r="F132" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
@@ -3517,17 +3554,17 @@
         <v>74802585268</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E133" s="1"/>
       <c r="F133" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
@@ -3535,15 +3572,15 @@
         <v>64074072149</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D134" s="4"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
@@ -3551,17 +3588,17 @@
         <v>3633872345</v>
       </c>
       <c r="B135" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D135" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D135" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
@@ -3569,17 +3606,17 @@
         <v>103076301</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E136" s="1"/>
       <c r="F136" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
@@ -3587,17 +3624,17 @@
         <v>1167202635</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E137" s="1"/>
       <c r="F137" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
@@ -3605,17 +3642,17 @@
         <v>56919069504</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E138" s="1"/>
       <c r="F138" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
@@ -3623,15 +3660,15 @@
         <v>13080839633</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C139" s="1"/>
       <c r="D139" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E139" s="1"/>
       <c r="F139" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
@@ -3639,17 +3676,17 @@
         <v>97485632515</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E140" s="1"/>
       <c r="F140" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
@@ -3658,14 +3695,14 @@
       </c>
       <c r="B141" s="1"/>
       <c r="C141" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E141" s="1"/>
       <c r="F141" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
@@ -3673,17 +3710,17 @@
         <v>7167052302</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E142" s="1"/>
       <c r="F142" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
@@ -3692,14 +3729,14 @@
       </c>
       <c r="B143" s="1"/>
       <c r="C143" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E143" s="1"/>
       <c r="F143" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
@@ -3708,14 +3745,14 @@
       </c>
       <c r="B144" s="1"/>
       <c r="C144" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E144" s="1"/>
       <c r="F144" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
@@ -3724,14 +3761,14 @@
       </c>
       <c r="B145" s="1"/>
       <c r="C145" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E145" s="1"/>
       <c r="F145" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
@@ -3740,14 +3777,14 @@
       </c>
       <c r="B146" s="1"/>
       <c r="C146" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E146" s="1"/>
       <c r="F146" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
@@ -3756,14 +3793,14 @@
       </c>
       <c r="B147" s="1"/>
       <c r="C147" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E147" s="1"/>
       <c r="F147" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
@@ -3771,15 +3808,15 @@
         <v>32298315191</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D148" s="4"/>
       <c r="E148" s="1"/>
       <c r="F148" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
@@ -3787,15 +3824,15 @@
         <v>8888285601</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D149" s="4"/>
       <c r="E149" s="1"/>
       <c r="F149" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
@@ -3803,17 +3840,17 @@
         <v>1615275401</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E150" s="1"/>
       <c r="F150" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
@@ -3821,15 +3858,15 @@
         <v>6011652760</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C151" s="1"/>
       <c r="D151" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E151" s="1"/>
       <c r="F151" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
@@ -3837,17 +3874,17 @@
         <v>57908893104</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E152" s="1"/>
       <c r="F152" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
@@ -3855,15 +3892,15 @@
         <v>70586931295</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C153" s="1"/>
       <c r="D153" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E153" s="1"/>
       <c r="F153" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
@@ -3871,15 +3908,15 @@
         <v>97407828253</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C154" s="1"/>
       <c r="D154" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E154" s="1"/>
       <c r="F154" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
@@ -3887,15 +3924,15 @@
         <v>3017306607</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C155" s="1"/>
       <c r="D155" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
@@ -3903,15 +3940,15 @@
         <v>11431230421</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C156" s="1"/>
       <c r="D156" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E156" s="1"/>
       <c r="F156" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
@@ -3919,15 +3956,15 @@
         <v>1705491359</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D157" s="4"/>
       <c r="E157" s="1"/>
       <c r="F157" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
@@ -3935,17 +3972,17 @@
         <v>92055613553</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E158" s="1"/>
       <c r="F158" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
@@ -3953,17 +3990,17 @@
         <v>4434895303</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E159" s="1"/>
       <c r="F159" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
@@ -3971,15 +4008,15 @@
         <v>5724205602</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D160" s="4"/>
       <c r="E160" s="1"/>
       <c r="F160" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
@@ -3987,17 +4024,17 @@
         <v>3670862048</v>
       </c>
       <c r="B161" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D161" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D161" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="E161" s="1"/>
       <c r="F161" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
@@ -4005,17 +4042,17 @@
         <v>8874532792</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E162" s="1"/>
       <c r="F162" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
@@ -4023,17 +4060,17 @@
         <v>62602713287</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E163" s="1"/>
       <c r="F163" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.3">
@@ -4042,28 +4079,30 @@
       </c>
       <c r="B164" s="1"/>
       <c r="C164" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E164" s="1"/>
       <c r="F164" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A165" s="2">
+      <c r="A165" s="18">
         <v>6062529248</v>
       </c>
-      <c r="B165" s="1"/>
-      <c r="C165" s="1"/>
-      <c r="D165" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E165" s="1"/>
-      <c r="F165" s="1" t="s">
-        <v>8</v>
+      <c r="B165" s="19"/>
+      <c r="C165" s="19"/>
+      <c r="D165" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E165" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F165" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
@@ -4072,14 +4111,14 @@
       </c>
       <c r="B166" s="1"/>
       <c r="C166" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E166" s="1"/>
       <c r="F166" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
@@ -4088,14 +4127,14 @@
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E167" s="1"/>
       <c r="F167" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
@@ -4104,14 +4143,14 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E168" s="1"/>
       <c r="F168" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
@@ -4119,15 +4158,15 @@
         <v>32762364</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="1"/>
       <c r="F169" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
@@ -4136,14 +4175,14 @@
       </c>
       <c r="B170" s="1"/>
       <c r="C170" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E170" s="1"/>
       <c r="F170" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
@@ -4152,12 +4191,12 @@
       </c>
       <c r="B171" s="1"/>
       <c r="C171" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D171" s="4"/>
       <c r="E171" s="1"/>
       <c r="F171" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
@@ -4166,14 +4205,14 @@
       </c>
       <c r="B172" s="1"/>
       <c r="C172" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E172" s="1"/>
       <c r="F172" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
@@ -4181,15 +4220,15 @@
         <v>995207</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D173" s="4"/>
       <c r="E173" s="1"/>
       <c r="F173" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
@@ -4197,15 +4236,15 @@
         <v>1322338</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D174" s="4"/>
       <c r="E174" s="1"/>
       <c r="F174" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
@@ -4214,12 +4253,12 @@
       </c>
       <c r="B175" s="1"/>
       <c r="C175" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="1"/>
       <c r="F175" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
@@ -4227,15 +4266,15 @@
         <v>54783321</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C176" s="1"/>
       <c r="D176" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E176" s="1"/>
       <c r="F176" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
@@ -4243,15 +4282,15 @@
         <v>187948313</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C177" s="1"/>
       <c r="D177" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E177" s="1"/>
       <c r="F177" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
@@ -4259,15 +4298,15 @@
         <v>1175017</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C178" s="1"/>
       <c r="D178" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E178" s="1"/>
       <c r="F178" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
@@ -4276,12 +4315,12 @@
       </c>
       <c r="B179" s="1"/>
       <c r="C179" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D179" s="4"/>
       <c r="E179" s="1"/>
       <c r="F179" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
@@ -4289,15 +4328,15 @@
         <v>19595905</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C180" s="1"/>
       <c r="D180" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E180" s="1"/>
       <c r="F180" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
@@ -4305,15 +4344,15 @@
         <v>72335319</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C181" s="1"/>
       <c r="D181" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E181" s="1"/>
       <c r="F181" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
@@ -4321,15 +4360,15 @@
         <v>141827343</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C182" s="1"/>
       <c r="D182" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E182" s="1"/>
       <c r="F182" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
@@ -4337,13 +4376,13 @@
         <v>152671307</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C183" s="1"/>
       <c r="D183" s="4"/>
       <c r="E183" s="1"/>
       <c r="F183" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
@@ -4351,15 +4390,15 @@
         <v>176295356</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C184" s="1"/>
       <c r="D184" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E184" s="1"/>
       <c r="F184" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
@@ -4367,13 +4406,13 @@
         <v>188854037</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C185" s="1"/>
       <c r="D185" s="4"/>
       <c r="E185" s="1"/>
       <c r="F185" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
@@ -4381,13 +4420,13 @@
         <v>261974050</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C186" s="1"/>
       <c r="D186" s="4"/>
       <c r="E186" s="1"/>
       <c r="F186" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
@@ -4395,15 +4434,15 @@
         <v>279698003</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C187" s="1"/>
       <c r="D187" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E187" s="1"/>
       <c r="F187" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
@@ -4411,13 +4450,13 @@
         <v>313186308</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C188" s="1"/>
       <c r="D188" s="4"/>
       <c r="E188" s="1"/>
       <c r="F188" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
@@ -4425,13 +4464,13 @@
         <v>342804057</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C189" s="1"/>
       <c r="D189" s="4"/>
       <c r="E189" s="1"/>
       <c r="F189" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
@@ -4439,13 +4478,13 @@
         <v>413071006</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C190" s="1"/>
       <c r="D190" s="4"/>
       <c r="E190" s="1"/>
       <c r="F190" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
@@ -4453,15 +4492,15 @@
         <v>415141222</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C191" s="1"/>
       <c r="D191" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E191" s="1"/>
       <c r="F191" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
@@ -4469,15 +4508,15 @@
         <v>420585540</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C192" s="1"/>
       <c r="D192" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E192" s="1"/>
       <c r="F192" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
@@ -4485,17 +4524,17 @@
         <v>90200551</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E193" s="1"/>
       <c r="F193" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
@@ -4503,17 +4542,17 @@
         <v>408855509</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E194" s="1"/>
       <c r="F194" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
@@ -4521,17 +4560,17 @@
         <v>3867409501</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E195" s="1"/>
       <c r="F195" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
@@ -4540,14 +4579,14 @@
       </c>
       <c r="B196" s="1"/>
       <c r="C196" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E196" s="1"/>
       <c r="F196" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
@@ -4555,17 +4594,17 @@
         <v>4723145486</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E197" s="1"/>
       <c r="F197" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
@@ -4573,13 +4612,13 @@
         <v>149071</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C198" s="1"/>
       <c r="D198" s="4"/>
       <c r="E198" s="1"/>
       <c r="F198" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
@@ -4587,15 +4626,15 @@
         <v>6272320</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C199" s="1"/>
       <c r="D199" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E199" s="1"/>
       <c r="F199" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
@@ -4603,15 +4642,15 @@
         <v>6313531</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C200" s="1"/>
       <c r="D200" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E200" s="1"/>
       <c r="F200" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
@@ -4619,13 +4658,13 @@
         <v>6340342</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C201" s="1"/>
       <c r="D201" s="4"/>
       <c r="E201" s="1"/>
       <c r="F201" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
@@ -4633,15 +4672,15 @@
         <v>7231342</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C202" s="1"/>
       <c r="D202" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E202" s="1"/>
       <c r="F202" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
@@ -4649,13 +4688,13 @@
         <v>11528311</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C203" s="1"/>
       <c r="D203" s="4"/>
       <c r="E203" s="1"/>
       <c r="F203" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
@@ -4665,11 +4704,11 @@
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
       <c r="D204" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E204" s="1"/>
       <c r="F204" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
@@ -4677,13 +4716,13 @@
         <v>308307</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C205" s="1"/>
       <c r="D205" s="4"/>
       <c r="E205" s="1"/>
       <c r="F205" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
@@ -4691,13 +4730,13 @@
         <v>2822350</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C206" s="1"/>
       <c r="D206" s="4"/>
       <c r="E206" s="1"/>
       <c r="F206" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
@@ -4705,13 +4744,13 @@
         <v>3469344</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C207" s="1"/>
       <c r="D207" s="4"/>
       <c r="E207" s="1"/>
       <c r="F207" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
@@ -4719,13 +4758,13 @@
         <v>4868250</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C208" s="1"/>
       <c r="D208" s="4"/>
       <c r="E208" s="1"/>
       <c r="F208" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
@@ -4734,12 +4773,12 @@
       </c>
       <c r="B209" s="1"/>
       <c r="C209" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D209" s="4"/>
       <c r="E209" s="1"/>
       <c r="F209" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
@@ -4747,13 +4786,13 @@
         <v>1450336</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C210" s="1"/>
       <c r="D210" s="4"/>
       <c r="E210" s="1"/>
       <c r="F210" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
@@ -4762,12 +4801,12 @@
       </c>
       <c r="B211" s="1"/>
       <c r="C211" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D211" s="4"/>
       <c r="E211" s="1"/>
       <c r="F211" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
@@ -4775,15 +4814,15 @@
         <v>2613352</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C212" s="1"/>
       <c r="D212" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E212" s="1"/>
       <c r="F212" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
@@ -4791,13 +4830,13 @@
         <v>2621533</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C213" s="1"/>
       <c r="D213" s="4"/>
       <c r="E213" s="1"/>
       <c r="F213" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
@@ -4805,15 +4844,15 @@
         <v>3708276</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C214" s="1"/>
       <c r="D214" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E214" s="1"/>
       <c r="F214" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
@@ -4823,11 +4862,11 @@
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
       <c r="D215" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E215" s="1"/>
       <c r="F215" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
@@ -4835,15 +4874,15 @@
         <v>636304</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C216" s="1"/>
       <c r="D216" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E216" s="1"/>
       <c r="F216" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
@@ -4852,12 +4891,12 @@
       </c>
       <c r="B217" s="1"/>
       <c r="C217" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D217" s="4"/>
       <c r="E217" s="1"/>
       <c r="F217" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
@@ -4865,13 +4904,13 @@
         <v>4889339</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C218" s="1"/>
       <c r="D218" s="4"/>
       <c r="E218" s="1"/>
       <c r="F218" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
@@ -4879,13 +4918,13 @@
         <v>5079381</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C219" s="1"/>
       <c r="D219" s="4"/>
       <c r="E219" s="1"/>
       <c r="F219" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
@@ -4893,13 +4932,13 @@
         <v>5114390</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C220" s="1"/>
       <c r="D220" s="4"/>
       <c r="E220" s="1"/>
       <c r="F220" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
@@ -4907,13 +4946,13 @@
         <v>5265339</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C221" s="1"/>
       <c r="D221" s="4"/>
       <c r="E221" s="1"/>
       <c r="F221" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
@@ -4922,26 +4961,28 @@
       </c>
       <c r="B222" s="1"/>
       <c r="C222" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D222" s="4"/>
       <c r="E222" s="1"/>
       <c r="F222" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A223" s="2">
+      <c r="A223" s="18">
         <v>42848369</v>
       </c>
-      <c r="B223" s="1"/>
-      <c r="C223" s="1"/>
-      <c r="D223" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E223" s="1"/>
-      <c r="F223" s="1" t="s">
-        <v>8</v>
+      <c r="B223" s="19"/>
+      <c r="C223" s="19"/>
+      <c r="D223" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E223" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F223" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
@@ -4950,14 +4991,14 @@
       </c>
       <c r="B224" s="1"/>
       <c r="C224" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E224" s="1"/>
       <c r="F224" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
@@ -4967,11 +5008,11 @@
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
       <c r="D225" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E225" s="1"/>
       <c r="F225" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
@@ -4979,13 +5020,13 @@
         <v>247862258</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C226" s="1"/>
       <c r="D226" s="4"/>
       <c r="E226" s="1"/>
       <c r="F226" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
@@ -4995,11 +5036,11 @@
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
       <c r="D227" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E227" s="1"/>
       <c r="F227" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
@@ -5009,11 +5050,11 @@
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
       <c r="D228" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E228" s="1"/>
       <c r="F228" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
@@ -5023,11 +5064,11 @@
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
       <c r="D229" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E229" s="1"/>
       <c r="F229" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
@@ -5037,11 +5078,11 @@
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
       <c r="D230" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E230" s="1"/>
       <c r="F230" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
@@ -5051,11 +5092,11 @@
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
       <c r="D231" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E231" s="1"/>
       <c r="F231" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
@@ -5064,12 +5105,12 @@
       </c>
       <c r="B232" s="1"/>
       <c r="C232" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D232" s="4"/>
       <c r="E232" s="1"/>
       <c r="F232" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
@@ -5078,14 +5119,14 @@
       </c>
       <c r="B233" s="1"/>
       <c r="C233" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E233" s="1"/>
       <c r="F233" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
@@ -5094,14 +5135,14 @@
       </c>
       <c r="B234" s="1"/>
       <c r="C234" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E234" s="1"/>
       <c r="F234" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.3">
@@ -5110,12 +5151,12 @@
       </c>
       <c r="B235" s="1"/>
       <c r="C235" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D235" s="4"/>
       <c r="E235" s="1"/>
       <c r="F235" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.3">
@@ -5124,12 +5165,12 @@
       </c>
       <c r="B236" s="1"/>
       <c r="C236" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D236" s="4"/>
       <c r="E236" s="1"/>
       <c r="F236" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
@@ -5137,13 +5178,13 @@
         <v>733487246</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C237" s="1"/>
       <c r="D237" s="4"/>
       <c r="E237" s="1"/>
       <c r="F237" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
@@ -5153,11 +5194,11 @@
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
       <c r="D238" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E238" s="1"/>
       <c r="F238" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.3">
@@ -5166,14 +5207,14 @@
       </c>
       <c r="B239" s="1"/>
       <c r="C239" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E239" s="1"/>
       <c r="F239" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
@@ -5183,11 +5224,11 @@
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
       <c r="D240" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E240" s="1"/>
       <c r="F240" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
@@ -5196,14 +5237,14 @@
       </c>
       <c r="B241" s="1"/>
       <c r="C241" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E241" s="1"/>
       <c r="F241" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
@@ -5211,29 +5252,29 @@
         <v>998175277</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C242" s="1"/>
       <c r="D242" s="4"/>
       <c r="E242" s="1"/>
       <c r="F242" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A243" s="21">
+      <c r="A243" s="18">
         <v>1104046377</v>
       </c>
-      <c r="B243" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C243" s="22"/>
-      <c r="D243" s="23"/>
-      <c r="E243" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F243" s="22" t="s">
-        <v>8</v>
+      <c r="B243" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C243" s="19"/>
+      <c r="D243" s="20"/>
+      <c r="E243" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F243" s="19" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
@@ -5242,12 +5283,12 @@
       </c>
       <c r="B244" s="1"/>
       <c r="C244" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D244" s="4"/>
       <c r="E244" s="1"/>
       <c r="F244" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.3">
@@ -5256,12 +5297,12 @@
       </c>
       <c r="B245" s="1"/>
       <c r="C245" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D245" s="4"/>
       <c r="E245" s="1"/>
       <c r="F245" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.3">
@@ -5270,14 +5311,14 @@
       </c>
       <c r="B246" s="1"/>
       <c r="C246" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E246" s="1"/>
       <c r="F246" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.3">
@@ -5287,11 +5328,11 @@
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
       <c r="D247" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E247" s="1"/>
       <c r="F247" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
@@ -5300,14 +5341,14 @@
       </c>
       <c r="B248" s="1"/>
       <c r="C248" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E248" s="1"/>
       <c r="F248" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
@@ -5315,31 +5356,29 @@
         <v>1316735214</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C249" s="1"/>
       <c r="D249" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E249" s="1"/>
       <c r="F249" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A250" s="21">
+      <c r="A250" s="30">
         <v>1327218305</v>
       </c>
-      <c r="B250" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C250" s="22"/>
-      <c r="D250" s="23"/>
-      <c r="E250" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F250" s="22" t="s">
-        <v>6</v>
+      <c r="B250" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="C250" s="31"/>
+      <c r="D250" s="32"/>
+      <c r="E250" s="31"/>
+      <c r="F250" s="31" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
@@ -5349,45 +5388,45 @@
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
       <c r="D251" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E251" s="1"/>
       <c r="F251" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A252" s="21">
+      <c r="A252" s="18">
         <v>1520317905</v>
       </c>
-      <c r="B252" s="22"/>
-      <c r="C252" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D252" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E252" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F252" s="22" t="s">
-        <v>6</v>
+      <c r="B252" s="19"/>
+      <c r="C252" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D252" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E252" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F252" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A253" s="21">
+      <c r="A253" s="18">
         <v>1552683257</v>
       </c>
-      <c r="B253" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C253" s="22"/>
-      <c r="D253" s="23"/>
-      <c r="E253" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F253" s="22" t="s">
-        <v>6</v>
+      <c r="B253" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C253" s="19"/>
+      <c r="D253" s="20"/>
+      <c r="E253" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F253" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.3">
@@ -5397,43 +5436,43 @@
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
       <c r="D254" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E254" s="1"/>
       <c r="F254" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A255" s="21">
+      <c r="A255" s="18">
         <v>1902803280</v>
       </c>
-      <c r="B255" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C255" s="22"/>
-      <c r="D255" s="23"/>
-      <c r="E255" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F255" s="22" t="s">
-        <v>6</v>
+      <c r="B255" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C255" s="19"/>
+      <c r="D255" s="20"/>
+      <c r="E255" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F255" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A256" s="21">
+      <c r="A256" s="18">
         <v>2045280624</v>
       </c>
-      <c r="B256" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C256" s="22"/>
-      <c r="D256" s="23"/>
-      <c r="E256" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F256" s="22" t="s">
-        <v>6</v>
+      <c r="B256" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C256" s="19"/>
+      <c r="D256" s="20"/>
+      <c r="E256" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F256" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.3">
@@ -5442,30 +5481,30 @@
       </c>
       <c r="B257" s="1"/>
       <c r="C257" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E257" s="1"/>
       <c r="F257" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A258" s="21">
+      <c r="A258" s="18">
         <v>2448337292</v>
       </c>
-      <c r="B258" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C258" s="22"/>
-      <c r="D258" s="23"/>
-      <c r="E258" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F258" s="22" t="s">
-        <v>6</v>
+      <c r="B258" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C258" s="19"/>
+      <c r="D258" s="20"/>
+      <c r="E258" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F258" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.3">
@@ -5474,12 +5513,12 @@
       </c>
       <c r="B259" s="1"/>
       <c r="C259" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D259" s="4"/>
       <c r="E259" s="1"/>
       <c r="F259" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
@@ -5489,27 +5528,27 @@
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
       <c r="D260" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E260" s="1"/>
       <c r="F260" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A261" s="21">
+      <c r="A261" s="18">
         <v>2668682665</v>
       </c>
-      <c r="B261" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C261" s="22"/>
-      <c r="D261" s="23"/>
-      <c r="E261" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F261" s="22" t="s">
-        <v>6</v>
+      <c r="B261" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C261" s="19"/>
+      <c r="D261" s="20"/>
+      <c r="E261" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F261" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
@@ -5519,11 +5558,11 @@
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
       <c r="D262" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E262" s="1"/>
       <c r="F262" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
@@ -5532,14 +5571,14 @@
       </c>
       <c r="B263" s="1"/>
       <c r="C263" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E263" s="1"/>
       <c r="F263" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
@@ -5549,43 +5588,43 @@
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
       <c r="D264" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E264" s="1"/>
       <c r="F264" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A265" s="21">
+      <c r="A265" s="18">
         <v>3001797150</v>
       </c>
-      <c r="B265" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C265" s="22"/>
-      <c r="D265" s="23"/>
-      <c r="E265" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F265" s="22" t="s">
-        <v>6</v>
+      <c r="B265" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C265" s="19"/>
+      <c r="D265" s="20"/>
+      <c r="E265" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F265" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A266" s="21">
+      <c r="A266" s="18">
         <v>3162488869</v>
       </c>
-      <c r="B266" s="22"/>
-      <c r="C266" s="22"/>
-      <c r="D266" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="E266" s="22" t="s">
-        <v>20</v>
-      </c>
-      <c r="F266" s="22" t="s">
-        <v>6</v>
+      <c r="B266" s="19"/>
+      <c r="C266" s="19"/>
+      <c r="D266" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E266" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F266" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5628,84 +5667,84 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="E1" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" s="9"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" s="9"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10" s="9"/>
     </row>
@@ -5781,489 +5820,494 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A07569E-5BDC-415E-ABD1-103C61B67D37}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" style="19" customWidth="1"/>
-    <col min="3" max="3" width="81.77734375" style="19" customWidth="1"/>
-    <col min="4" max="4" width="15.44140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="17" customWidth="1"/>
+    <col min="3" max="3" width="81.77734375" style="17" customWidth="1"/>
+    <col min="4" max="4" width="15.44140625" style="17" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="24" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A2" s="21">
+        <v>1</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="21">
+        <v>2</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="30" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="24">
+      <c r="C3" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A4" s="33">
+        <v>3</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="36">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="33">
+        <v>4</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="21">
+        <v>5</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="33">
+        <v>6</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="33">
+        <v>7</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="33">
+        <v>8</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A10" s="25">
+        <v>9</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="25">
+        <v>10</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="21">
+        <v>11</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A13" s="21">
+        <v>12</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A14" s="21">
+        <v>13</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="21">
+        <v>14</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="25">
+        <v>15</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="25">
+        <v>16</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="28">
         <v>1</v>
       </c>
-      <c r="B2" s="25" t="s">
+    </row>
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="25">
+        <v>17</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="25">
+        <v>18</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A20" s="33">
+        <v>19</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" s="33">
+        <v>20</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+      <c r="A22" s="37">
+        <v>21</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="37">
+        <v>22</v>
+      </c>
+      <c r="B23" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="37">
+        <v>23</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E24" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="37">
+        <v>24</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="37">
+        <v>25</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="D26" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="37">
+        <v>26</v>
+      </c>
+      <c r="B27" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="35">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24">
-        <v>2</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="35">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="24">
-        <v>3</v>
-      </c>
-      <c r="B4" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E4" s="35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24">
-        <v>4</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="24">
-        <v>5</v>
-      </c>
-      <c r="B6" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="27">
-        <v>6</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="E7" s="34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27">
-        <v>7</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="31">
-        <v>8</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="31">
-        <v>9</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E10" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="31">
-        <v>10</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="31">
-        <v>11</v>
-      </c>
-      <c r="B12" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
-        <v>12</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" s="9"/>
-    </row>
-    <row r="14" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
-        <v>13</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="9"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="17">
-        <v>14</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="9"/>
-    </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="31">
-        <v>15</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="31">
-        <v>16</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E17" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="31">
-        <v>17</v>
-      </c>
-      <c r="B18" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E18" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="31">
-        <v>18</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E19" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="31">
-        <v>18</v>
-      </c>
-      <c r="B20" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E20" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="17">
-        <v>20</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="31">
-        <v>21</v>
-      </c>
-      <c r="B22" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="31">
-        <v>22</v>
-      </c>
-      <c r="B23" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E23" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="17">
-        <v>23</v>
-      </c>
-      <c r="B24" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="9"/>
-    </row>
-    <row r="25" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="17">
-        <v>24</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="9"/>
-    </row>
-    <row r="26" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="31">
-        <v>25</v>
-      </c>
-      <c r="B26" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C26" s="33" t="s">
+      <c r="C27" s="39" t="s">
         <v>63</v>
       </c>
-      <c r="D26" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="31">
-        <v>26</v>
-      </c>
-      <c r="B27" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E27" s="34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="31">
+      <c r="D27" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="37">
         <v>27</v>
       </c>
-      <c r="B28" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="C28" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="D28" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="E28" s="34">
-        <v>1</v>
+      <c r="B28" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="40">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D28" xr:uid="{9A07569E-5BDC-415E-ABD1-103C61B67D37}">
-    <filterColumn colId="0">
-      <filters blank="1">
-        <filter val="NÃO EXECUTADO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="D1:D28" xr:uid="{9A07569E-5BDC-415E-ABD1-103C61B67D37}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -6295,25 +6339,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>46</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -6365,15 +6409,27 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="A4" s="12">
+        <v>0.64861111111111114</v>
+      </c>
+      <c r="B4" s="13">
+        <v>46253</v>
+      </c>
+      <c r="C4" s="14">
+        <v>7</v>
+      </c>
+      <c r="D4" s="14">
+        <v>7</v>
+      </c>
+      <c r="E4" s="14">
+        <v>7</v>
+      </c>
+      <c r="F4" s="14">
+        <v>6</v>
+      </c>
       <c r="G4" s="15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740CBD6E-48FA-47B0-A4A9-9573F5272250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F0C437-60BB-475C-A084-62F2BCE039C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Massa_HML_B31_FLUXO_INTEGRADO" sheetId="3" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="71">
   <si>
     <t>CPF</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t>Possui período validado</t>
+  </si>
+  <si>
+    <t>Ag Reteste</t>
   </si>
 </sst>
 </file>
@@ -460,7 +463,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -673,6 +676,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -904,7 +919,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -990,6 +1005,26 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2634,39 +2669,43 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="2">
+      <c r="A75" s="18">
         <v>979170796</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D75" s="4" t="s">
+      <c r="B75" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1" t="s">
-        <v>7</v>
+      <c r="E75" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="2">
+      <c r="A76" s="18">
         <v>1017978506</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D76" s="4" t="s">
+      <c r="B76" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1" t="s">
-        <v>7</v>
+      <c r="E76" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F76" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -2700,19 +2739,21 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="2">
+      <c r="A79" s="18">
         <v>692565</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C79" s="1"/>
-      <c r="D79" s="4" t="s">
+      <c r="B79" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="19"/>
+      <c r="D79" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1" t="s">
-        <v>7</v>
+      <c r="E79" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F79" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -5174,17 +5215,19 @@
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A237" s="2">
+      <c r="A237" s="18">
         <v>733487246</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C237" s="1"/>
-      <c r="D237" s="4"/>
-      <c r="E237" s="1"/>
-      <c r="F237" s="1" t="s">
-        <v>7</v>
+      <c r="B237" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C237" s="19"/>
+      <c r="D237" s="20"/>
+      <c r="E237" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F237" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.3">
@@ -5248,17 +5291,19 @@
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A242" s="2">
+      <c r="A242" s="18">
         <v>998175277</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C242" s="1"/>
-      <c r="D242" s="4"/>
-      <c r="E242" s="1"/>
-      <c r="F242" s="1" t="s">
-        <v>7</v>
+      <c r="B242" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C242" s="19"/>
+      <c r="D242" s="20"/>
+      <c r="E242" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F242" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.3">
@@ -5522,17 +5567,19 @@
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A260" s="2">
+      <c r="A260" s="18">
         <v>2564074286</v>
       </c>
-      <c r="B260" s="1"/>
-      <c r="C260" s="1"/>
-      <c r="D260" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E260" s="1"/>
-      <c r="F260" s="1" t="s">
-        <v>7</v>
+      <c r="B260" s="19"/>
+      <c r="C260" s="19"/>
+      <c r="D260" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E260" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F260" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.3">
@@ -5552,33 +5599,37 @@
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A262" s="2">
+      <c r="A262" s="18">
         <v>2705278931</v>
       </c>
-      <c r="B262" s="1"/>
-      <c r="C262" s="1"/>
-      <c r="D262" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E262" s="1"/>
-      <c r="F262" s="1" t="s">
-        <v>7</v>
+      <c r="B262" s="19"/>
+      <c r="C262" s="19"/>
+      <c r="D262" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E262" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F262" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A263" s="2">
+      <c r="A263" s="18">
         <v>2792829826</v>
       </c>
-      <c r="B263" s="1"/>
-      <c r="C263" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D263" s="4" t="s">
+      <c r="B263" s="19"/>
+      <c r="C263" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D263" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E263" s="1"/>
-      <c r="F263" s="1" t="s">
-        <v>7</v>
+      <c r="E263" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F263" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.3">
@@ -5865,53 +5916,53 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="21">
+      <c r="A3" s="41">
         <v>2</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="29">
+      <c r="D3" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" s="44">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="33">
+      <c r="A4" s="41">
         <v>3</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="36">
+      <c r="D4" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" s="44">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="33">
+      <c r="A5" s="41">
         <v>4</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="36">
+      <c r="D5" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="44">
         <v>5</v>
       </c>
     </row>
@@ -6116,7 +6167,7 @@
         <v>39</v>
       </c>
       <c r="E17" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -6133,24 +6184,24 @@
         <v>39</v>
       </c>
       <c r="E18" s="28">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="25">
+      <c r="A19" s="33">
         <v>18</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="28">
-        <v>1</v>
+      <c r="D19" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="36">
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="72" x14ac:dyDescent="0.3">
@@ -6222,37 +6273,37 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="37">
+      <c r="A24" s="45">
         <v>23</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="39" t="s">
+      <c r="C24" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="40">
-        <v>0</v>
+      <c r="D24" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="48">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="37">
+      <c r="A25" s="45">
         <v>24</v>
       </c>
-      <c r="B25" s="38" t="s">
+      <c r="B25" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="39" t="s">
+      <c r="C25" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="40">
-        <v>0</v>
+      <c r="D25" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="48">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
@@ -6326,18 +6377,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABD6A9E0-399C-4737-BBBE-100AAF3BE286}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" customWidth="1"/>
     <col min="3" max="3" width="15.88671875" customWidth="1"/>
     <col min="4" max="4" width="12.88671875" customWidth="1"/>
-    <col min="5" max="5" width="15.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1"/>
+    <col min="5" max="6" width="15.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>40</v>
       </c>
@@ -6354,13 +6405,16 @@
         <v>44</v>
       </c>
       <c r="F1" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>0.41666666666666669</v>
       </c>
@@ -6379,12 +6433,15 @@
       <c r="F2" s="14">
         <v>0</v>
       </c>
-      <c r="G2" s="15">
-        <f>C2+D2+E2+F2</f>
+      <c r="G2" s="14">
+        <v>0</v>
+      </c>
+      <c r="H2" s="15">
+        <f>C2+D2+E2+G2+F2</f>
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="12">
         <v>11</v>
       </c>
@@ -6401,46 +6458,53 @@
         <v>0</v>
       </c>
       <c r="F3" s="14">
+        <v>0</v>
+      </c>
+      <c r="G3" s="14">
         <v>16</v>
       </c>
-      <c r="G3" s="15">
-        <f t="shared" ref="G3:G5" si="0">C3+D3+E3+F3</f>
+      <c r="H3" s="15">
+        <f>C3+D3+E3+G3+F3</f>
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="12">
-        <v>0.64861111111111114</v>
+        <v>0.69791666666666663</v>
       </c>
       <c r="B4" s="13">
         <v>46253</v>
       </c>
       <c r="C4" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="14">
-        <v>6</v>
-      </c>
-      <c r="G4" s="15">
-        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="G4" s="14">
+        <v>7</v>
+      </c>
+      <c r="H4" s="15">
+        <f>C4+D4+E4+G4+F4</f>
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="12"/>
       <c r="B5" s="13"/>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
-      <c r="G5" s="15">
-        <f t="shared" si="0"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="15">
+        <f t="shared" ref="H3:H5" si="0">C5+D5+E5+G5</f>
         <v>0</v>
       </c>
     </row>

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F0C437-60BB-475C-A084-62F2BCE039C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75585B74-C5A3-460B-A18B-E29A3DD431C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Massa_HML_B31_FLUXO_INTEGRADO" sheetId="3" r:id="rId1"/>
@@ -6239,37 +6239,37 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A22" s="37">
+      <c r="A22" s="45">
         <v>21</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="39" t="s">
+      <c r="C22" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="40">
-        <v>0</v>
+      <c r="D22" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="48">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="37">
+      <c r="A23" s="45">
         <v>22</v>
       </c>
-      <c r="B23" s="38" t="s">
+      <c r="B23" s="46" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="39" t="s">
+      <c r="C23" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="40">
-        <v>0</v>
+      <c r="D23" s="45" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="48">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -6496,16 +6496,30 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
+      <c r="A5" s="12">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="B5" s="13">
+        <v>46254</v>
+      </c>
+      <c r="C5" s="14">
+        <v>3</v>
+      </c>
+      <c r="D5" s="14">
+        <v>6</v>
+      </c>
+      <c r="E5" s="14">
+        <v>6</v>
+      </c>
+      <c r="F5" s="14">
+        <v>3</v>
+      </c>
+      <c r="G5" s="14">
+        <v>9</v>
+      </c>
       <c r="H5" s="15">
-        <f t="shared" ref="H3:H5" si="0">C5+D5+E5+G5</f>
-        <v>0</v>
+        <f>C5+D5+E5+G5+F5</f>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75585B74-C5A3-460B-A18B-E29A3DD431C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48E165F-6EB5-4B7E-98A5-22369DBE6F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
@@ -6307,20 +6307,20 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="37">
+      <c r="A26" s="33">
         <v>25</v>
       </c>
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="39" t="s">
+      <c r="C26" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="40">
-        <v>0</v>
+      <c r="D26" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="36">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
@@ -6503,13 +6503,13 @@
         <v>46254</v>
       </c>
       <c r="C5" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5" s="14">
         <v>6</v>
       </c>
       <c r="E5" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" s="14">
         <v>3</v>

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F48E165F-6EB5-4B7E-98A5-22369DBE6F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEA07A8-1763-49A2-88F0-24BB7063A320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="71">
   <si>
     <t>CPF</t>
   </si>
@@ -919,7 +919,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -995,16 +995,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1759,19 +1749,17 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="18">
+      <c r="A21" s="30">
         <v>4024368818</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="20"/>
-      <c r="E21" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>5</v>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="32"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
@@ -2289,19 +2277,21 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="2">
+      <c r="A52" s="18">
         <v>93573006</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="4"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1" t="s">
-        <v>7</v>
+      <c r="B52" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="20"/>
+      <c r="E52" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2453,17 +2443,19 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="2">
+      <c r="A62" s="18">
         <v>2184685550</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" s="1"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1" t="s">
-        <v>7</v>
+      <c r="B62" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="19"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -2709,33 +2701,37 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="2">
+      <c r="A77" s="18">
         <v>94893438549</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C77" s="1"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1" t="s">
-        <v>7</v>
+      <c r="B77" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" s="19"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="2">
+      <c r="A78" s="18">
         <v>375322</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="4" t="s">
+      <c r="B78" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="19"/>
+      <c r="D78" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1" t="s">
-        <v>7</v>
+      <c r="E78" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F78" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -2875,121 +2871,137 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="2">
+      <c r="A87" s="18">
         <v>9229</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C87" s="1"/>
-      <c r="D87" s="4" t="s">
+      <c r="B87" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="19"/>
+      <c r="D87" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1" t="s">
-        <v>7</v>
+      <c r="E87" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F87" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="2">
+      <c r="A88" s="18">
         <v>160202</v>
       </c>
-      <c r="B88" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C88" s="1"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1" t="s">
-        <v>7</v>
+      <c r="B88" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="19"/>
+      <c r="D88" s="20"/>
+      <c r="E88" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="2">
+      <c r="A89" s="18">
         <v>176044</v>
       </c>
-      <c r="B89" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" s="1"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1" t="s">
-        <v>7</v>
+      <c r="B89" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="19"/>
+      <c r="D89" s="20"/>
+      <c r="E89" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F89" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="2">
+      <c r="A90" s="18">
         <v>352381</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C90" s="1"/>
-      <c r="D90" s="4" t="s">
+      <c r="B90" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="19"/>
+      <c r="D90" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1" t="s">
-        <v>7</v>
+      <c r="E90" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F90" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="2">
+      <c r="A91" s="18">
         <v>1109570</v>
       </c>
-      <c r="B91" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C91" s="1"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1" t="s">
-        <v>7</v>
+      <c r="B91" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="19"/>
+      <c r="D91" s="20"/>
+      <c r="E91" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F91" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="2">
+      <c r="A92" s="18">
         <v>1220330</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C92" s="1"/>
-      <c r="D92" s="4" t="s">
+      <c r="B92" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="19"/>
+      <c r="D92" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1" t="s">
-        <v>7</v>
+      <c r="E92" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F92" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="2">
+      <c r="A93" s="18">
         <v>60129750310</v>
       </c>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D93" s="4"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1" t="s">
-        <v>7</v>
+      <c r="B93" s="19"/>
+      <c r="C93" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" s="20"/>
+      <c r="E93" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F93" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="2">
+      <c r="A94" s="18">
         <v>63707777308</v>
       </c>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D94" s="4"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1" t="s">
-        <v>7</v>
+      <c r="B94" s="19"/>
+      <c r="C94" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" s="20"/>
+      <c r="E94" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F94" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3165,17 +3177,19 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="2">
+      <c r="A106" s="18">
         <v>6626238</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C106" s="1"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1" t="s">
-        <v>7</v>
+      <c r="B106" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C106" s="19"/>
+      <c r="D106" s="20"/>
+      <c r="E106" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F106" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -5319,7 +5333,7 @@
         <v>19</v>
       </c>
       <c r="F243" s="19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.3">
@@ -5381,19 +5395,21 @@
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A248" s="2">
+      <c r="A248" s="18">
         <v>1313908215</v>
       </c>
-      <c r="B248" s="1"/>
-      <c r="C248" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D248" s="4" t="s">
+      <c r="B248" s="19"/>
+      <c r="C248" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D248" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E248" s="1"/>
-      <c r="F248" s="1" t="s">
-        <v>7</v>
+      <c r="E248" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F248" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.3">
@@ -5427,17 +5443,19 @@
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A251" s="2">
+      <c r="A251" s="18">
         <v>1469330792</v>
       </c>
-      <c r="B251" s="1"/>
-      <c r="C251" s="1"/>
-      <c r="D251" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E251" s="1"/>
-      <c r="F251" s="1" t="s">
-        <v>7</v>
+      <c r="B251" s="19"/>
+      <c r="C251" s="19"/>
+      <c r="D251" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E251" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F251" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.3">
@@ -5871,6 +5889,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A07569E-5BDC-415E-ABD1-103C61B67D37}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5898,7 +5917,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="21">
         <v>1</v>
       </c>
@@ -5915,58 +5934,58 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="41">
+    <row r="3" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="37">
         <v>2</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="44">
+      <c r="E3" s="40">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A4" s="41">
+    <row r="4" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="37">
         <v>3</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="40">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="41">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="37">
         <v>4</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="44">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E5" s="40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="21">
         <v>5</v>
       </c>
@@ -5980,75 +5999,75 @@
         <v>35</v>
       </c>
       <c r="E6" s="29">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21">
         <v>6</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" s="33">
-        <v>7</v>
-      </c>
-      <c r="B8" s="34" t="s">
+      <c r="D7" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="21">
+        <v>7</v>
+      </c>
+      <c r="B8" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="33">
+      <c r="D8" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21">
         <v>8</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="B9" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A10" s="25">
+      <c r="D9" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="29">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="37">
         <v>9</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="28">
-        <v>5</v>
+      <c r="D10" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="40">
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
@@ -6065,10 +6084,10 @@
         <v>39</v>
       </c>
       <c r="E11" s="28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="21">
         <v>11</v>
       </c>
@@ -6082,10 +6101,10 @@
         <v>35</v>
       </c>
       <c r="E12" s="29">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="21">
         <v>12</v>
       </c>
@@ -6099,10 +6118,10 @@
         <v>35</v>
       </c>
       <c r="E13" s="29">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="21">
         <v>13</v>
       </c>
@@ -6116,10 +6135,10 @@
         <v>35</v>
       </c>
       <c r="E14" s="29">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21">
         <v>14</v>
       </c>
@@ -6133,24 +6152,24 @@
         <v>35</v>
       </c>
       <c r="E15" s="29">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="21">
         <v>15</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="28">
-        <v>2</v>
+      <c r="D16" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="29">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -6170,24 +6189,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="25">
+    <row r="18" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="37">
         <v>17</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="28">
+      <c r="D18" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="40">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>18</v>
       </c>
@@ -6205,160 +6224,166 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A20" s="33">
+      <c r="A20" s="25">
         <v>19</v>
       </c>
-      <c r="B20" s="34" t="s">
+      <c r="B20" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="35" t="s">
+      <c r="C20" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="36">
+      <c r="D20" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A21" s="33">
+      <c r="A21" s="25">
         <v>20</v>
       </c>
-      <c r="B21" s="34" t="s">
+      <c r="B21" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="35" t="s">
+      <c r="C21" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="36">
+      <c r="D21" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A22" s="45">
+      <c r="A22" s="41">
         <v>21</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="47" t="s">
+      <c r="C22" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="45" t="s">
+      <c r="D22" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="E22" s="48">
+      <c r="E22" s="44">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="45">
+      <c r="A23" s="41">
         <v>22</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="47" t="s">
+      <c r="C23" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="45" t="s">
+      <c r="D23" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="E23" s="48">
+      <c r="E23" s="44">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="45">
+      <c r="A24" s="41">
         <v>23</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="47" t="s">
+      <c r="C24" s="43" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="45" t="s">
+      <c r="D24" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="48">
+      <c r="E24" s="44">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="45">
+      <c r="A25" s="41">
         <v>24</v>
       </c>
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="47" t="s">
+      <c r="C25" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="45" t="s">
+      <c r="D25" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="48">
+      <c r="E25" s="44">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="33">
+      <c r="A26" s="25">
         <v>25</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="35" t="s">
+      <c r="C26" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" s="36">
+      <c r="D26" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="37">
+      <c r="A27" s="25">
         <v>26</v>
       </c>
-      <c r="B27" s="38" t="s">
+      <c r="B27" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="39" t="s">
+      <c r="C27" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="40">
-        <v>0</v>
+      <c r="D27" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="28">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="37">
+      <c r="A28" s="25">
         <v>27</v>
       </c>
-      <c r="B28" s="38" t="s">
+      <c r="B28" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="37" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="40">
-        <v>0</v>
+      <c r="D28" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="28">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D28" xr:uid="{9A07569E-5BDC-415E-ABD1-103C61B67D37}"/>
+  <autoFilter ref="D1:D28" xr:uid="{9A07569E-5BDC-415E-ABD1-103C61B67D37}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="EM TESTE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -6497,25 +6522,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
-        <v>0.45833333333333331</v>
+        <v>0.69930555555555551</v>
       </c>
       <c r="B5" s="13">
         <v>46254</v>
       </c>
       <c r="C5" s="14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D5" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E5" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F5" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H5" s="15">
         <f>C5+D5+E5+G5+F5</f>

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEA07A8-1763-49A2-88F0-24BB7063A320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70E7D14-7EC5-4C72-AFE3-0E3C07279779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Massa_HML_B31_FLUXO_INTEGRADO" sheetId="3" r:id="rId1"/>
@@ -20,6 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">CENARIOS!$D$1:$D$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Massa_HML_B31_FLUXO_INTEGRADO!$A$1:$F$266</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="71">
   <si>
     <t>CPF</t>
   </si>
@@ -463,7 +464,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="40">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -676,12 +677,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -919,7 +914,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -985,16 +980,6 @@
     <xf numFmtId="164" fontId="0" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1005,16 +990,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1381,6 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834A0C64-4F07-424E-993E-2EA5E6BA9836}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F266"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1461,7 +1437,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1711,7 +1687,7 @@
         <v>15</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -1748,7 +1724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="30">
         <v>4024368818</v>
       </c>
@@ -1908,7 +1884,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>17713986987</v>
       </c>
@@ -1924,7 +1900,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>20404965806</v>
       </c>
@@ -2014,7 +1990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>87764997404</v>
       </c>
@@ -2066,7 +2042,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>9366261</v>
       </c>
@@ -2082,7 +2058,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>1548301</v>
       </c>
@@ -2098,7 +2074,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>1818384</v>
       </c>
@@ -2114,7 +2090,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>59054271</v>
       </c>
@@ -2130,7 +2106,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>65913299</v>
       </c>
@@ -2146,7 +2122,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>79277209</v>
       </c>
@@ -2162,7 +2138,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>79682219</v>
       </c>
@@ -2176,7 +2152,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>102850240</v>
       </c>
@@ -2190,7 +2166,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>114745218</v>
       </c>
@@ -2206,7 +2182,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>7227906</v>
       </c>
@@ -2240,7 +2216,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>10152148</v>
       </c>
@@ -2258,7 +2234,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>61461121</v>
       </c>
@@ -2294,7 +2270,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>95026100</v>
       </c>
@@ -2310,7 +2286,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>7494173404</v>
       </c>
@@ -2328,7 +2304,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>7496954390</v>
       </c>
@@ -2346,7 +2322,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>7502772383</v>
       </c>
@@ -2381,22 +2357,24 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="2">
+      <c r="A58" s="18">
         <v>251275</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C58" s="1"/>
-      <c r="D58" s="4" t="s">
+      <c r="B58" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="19"/>
+      <c r="D58" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E58" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>40999408</v>
       </c>
@@ -2412,7 +2390,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>52062511</v>
       </c>
@@ -2426,7 +2404,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>96619309</v>
       </c>
@@ -2458,7 +2436,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>136679390</v>
       </c>
@@ -2476,7 +2454,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>284905330</v>
       </c>
@@ -2492,7 +2470,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>404822606</v>
       </c>
@@ -2510,7 +2488,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>455785163</v>
       </c>
@@ -2528,7 +2506,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>485318989</v>
       </c>
@@ -2544,7 +2522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>98983768304</v>
       </c>
@@ -2558,7 +2536,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>99052210349</v>
       </c>
@@ -2574,7 +2552,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>99178826500</v>
       </c>
@@ -2588,7 +2566,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>99447444504</v>
       </c>
@@ -2753,22 +2731,24 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="2">
+      <c r="A80" s="18">
         <v>867039</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C80" s="1"/>
-      <c r="D80" s="4" t="s">
+      <c r="B80" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="19"/>
+      <c r="D80" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E80" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F80" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>9955937289</v>
       </c>
@@ -2784,7 +2764,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>15930796998</v>
       </c>
@@ -2803,22 +2783,24 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="2">
+      <c r="A83" s="18">
         <v>15930802980</v>
       </c>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D83" s="4" t="s">
+      <c r="B83" s="19"/>
+      <c r="C83" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E83" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F83" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>20603332889</v>
       </c>
@@ -2835,39 +2817,43 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="2">
+      <c r="A85" s="18">
         <v>31828499803</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D85" s="4" t="s">
+      <c r="B85" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1" t="s">
-        <v>7</v>
+      <c r="E85" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F85" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="2">
+      <c r="A86" s="18">
         <v>75424460291</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D86" s="4" t="s">
+      <c r="B86" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1" t="s">
-        <v>7</v>
+      <c r="E86" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F86" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -3004,7 +2990,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>94410984349</v>
       </c>
@@ -3018,7 +3004,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>1943263302</v>
       </c>
@@ -3034,7 +3020,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>3293140335</v>
       </c>
@@ -3050,7 +3036,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>11302822365</v>
       </c>
@@ -3082,7 +3068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>49293710153</v>
       </c>
@@ -3096,7 +3082,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>62206311615</v>
       </c>
@@ -3112,7 +3098,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>1409107</v>
       </c>
@@ -3128,7 +3114,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>1455133</v>
       </c>
@@ -3144,7 +3130,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>1524208</v>
       </c>
@@ -3160,7 +3146,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>5165202</v>
       </c>
@@ -3192,7 +3178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>1754503586</v>
       </c>
@@ -3210,7 +3196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>2820058205</v>
       </c>
@@ -3226,7 +3212,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>4099781674</v>
       </c>
@@ -3243,19 +3229,21 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="2">
+      <c r="A110" s="18">
         <v>5485659101</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C110" s="1"/>
-      <c r="D110" s="4" t="s">
+      <c r="B110" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C110" s="19"/>
+      <c r="D110" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E110" s="1"/>
-      <c r="F110" s="1" t="s">
-        <v>7</v>
+      <c r="E110" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F110" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
@@ -3290,7 +3278,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>1872891071</v>
       </c>
@@ -3308,7 +3296,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>6300019446</v>
       </c>
@@ -3322,7 +3310,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>7297222445</v>
       </c>
@@ -3368,7 +3356,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>1827618</v>
       </c>
@@ -3382,7 +3370,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>1834584</v>
       </c>
@@ -3399,20 +3387,22 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="2">
+      <c r="A120" s="18">
         <v>17382940802</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C120" s="1"/>
-      <c r="D120" s="4"/>
-      <c r="E120" s="1"/>
-      <c r="F120" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B120" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C120" s="19"/>
+      <c r="D120" s="20"/>
+      <c r="E120" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F120" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>61707357323</v>
       </c>
@@ -3427,22 +3417,24 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="2">
+      <c r="A122" s="18">
         <v>5361133</v>
       </c>
-      <c r="B122" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C122" s="1"/>
-      <c r="D122" s="4" t="s">
+      <c r="B122" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C122" s="19"/>
+      <c r="D122" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E122" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F122" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>11194359</v>
       </c>
@@ -3458,7 +3450,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>35324376</v>
       </c>
@@ -3474,7 +3466,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>36184390</v>
       </c>
@@ -3490,7 +3482,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>92359426320</v>
       </c>
@@ -3506,7 +3498,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>2149575</v>
       </c>
@@ -3522,7 +3514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>3382076519</v>
       </c>
@@ -3538,7 +3530,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>56905580520</v>
       </c>
@@ -3554,7 +3546,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>284471313</v>
       </c>
@@ -3572,7 +3564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>95044353191</v>
       </c>
@@ -3588,7 +3580,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>87026902172</v>
       </c>
@@ -3604,7 +3596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>74802585268</v>
       </c>
@@ -3622,7 +3614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>64074072149</v>
       </c>
@@ -3638,7 +3630,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>3633872345</v>
       </c>
@@ -3656,7 +3648,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>103076301</v>
       </c>
@@ -3674,7 +3666,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>1167202635</v>
       </c>
@@ -3692,7 +3684,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>56919069504</v>
       </c>
@@ -3710,7 +3702,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>13080839633</v>
       </c>
@@ -3726,7 +3718,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>97485632515</v>
       </c>
@@ -3744,7 +3736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>11202344410</v>
       </c>
@@ -3760,7 +3752,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>7167052302</v>
       </c>
@@ -3778,7 +3770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>6398143604</v>
       </c>
@@ -3794,7 +3786,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>2331911355</v>
       </c>
@@ -3810,7 +3802,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>16874878638</v>
       </c>
@@ -3826,7 +3818,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>44367066304</v>
       </c>
@@ -3842,7 +3834,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>46272803869</v>
       </c>
@@ -3858,7 +3850,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>32298315191</v>
       </c>
@@ -3874,7 +3866,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>8888285601</v>
       </c>
@@ -3890,7 +3882,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>1615275401</v>
       </c>
@@ -3908,7 +3900,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>6011652760</v>
       </c>
@@ -3924,7 +3916,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>57908893104</v>
       </c>
@@ -3942,7 +3934,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>70586931295</v>
       </c>
@@ -3958,7 +3950,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>97407828253</v>
       </c>
@@ -3974,7 +3966,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>3017306607</v>
       </c>
@@ -3990,7 +3982,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>11431230421</v>
       </c>
@@ -4006,7 +3998,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>1705491359</v>
       </c>
@@ -4022,7 +4014,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>92055613553</v>
       </c>
@@ -4040,7 +4032,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>4434895303</v>
       </c>
@@ -4058,7 +4050,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>5724205602</v>
       </c>
@@ -4074,7 +4066,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>3670862048</v>
       </c>
@@ -4092,7 +4084,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>8874532792</v>
       </c>
@@ -4110,7 +4102,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>62602713287</v>
       </c>
@@ -4128,7 +4120,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>9006781940</v>
       </c>
@@ -4160,7 +4152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>11652859918</v>
       </c>
@@ -4176,7 +4168,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>14693733601</v>
       </c>
@@ -4192,7 +4184,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>93842155620</v>
       </c>
@@ -4208,7 +4200,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>32762364</v>
       </c>
@@ -4224,7 +4216,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>38628015</v>
       </c>
@@ -4240,7 +4232,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>71667377</v>
       </c>
@@ -4254,7 +4246,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>251356</v>
       </c>
@@ -4270,7 +4262,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="2">
         <v>995207</v>
       </c>
@@ -4286,7 +4278,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="2">
         <v>1322338</v>
       </c>
@@ -4302,7 +4294,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="2">
         <v>5211913</v>
       </c>
@@ -4316,7 +4308,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="2">
         <v>54783321</v>
       </c>
@@ -4332,7 +4324,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="2">
         <v>187948313</v>
       </c>
@@ -4348,7 +4340,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="2">
         <v>1175017</v>
       </c>
@@ -4364,7 +4356,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="2">
         <v>13693778</v>
       </c>
@@ -4378,7 +4370,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="2">
         <v>19595905</v>
       </c>
@@ -4394,7 +4386,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2">
         <v>72335319</v>
       </c>
@@ -4410,7 +4402,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="2">
         <v>141827343</v>
       </c>
@@ -4426,7 +4418,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2">
         <v>152671307</v>
       </c>
@@ -4440,7 +4432,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="2">
         <v>176295356</v>
       </c>
@@ -4456,7 +4448,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2">
         <v>188854037</v>
       </c>
@@ -4471,78 +4463,88 @@
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A186" s="2">
+      <c r="A186" s="18">
         <v>261974050</v>
       </c>
-      <c r="B186" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C186" s="1"/>
-      <c r="D186" s="4"/>
-      <c r="E186" s="1"/>
-      <c r="F186" s="1" t="s">
-        <v>7</v>
+      <c r="B186" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C186" s="19"/>
+      <c r="D186" s="20"/>
+      <c r="E186" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F186" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A187" s="2">
+      <c r="A187" s="18">
         <v>279698003</v>
       </c>
-      <c r="B187" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C187" s="1"/>
-      <c r="D187" s="4" t="s">
+      <c r="B187" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C187" s="19"/>
+      <c r="D187" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E187" s="1"/>
-      <c r="F187" s="1" t="s">
-        <v>7</v>
+      <c r="E187" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F187" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A188" s="2">
+      <c r="A188" s="18">
         <v>313186308</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C188" s="1"/>
-      <c r="D188" s="4"/>
-      <c r="E188" s="1"/>
-      <c r="F188" s="1" t="s">
-        <v>7</v>
+      <c r="B188" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C188" s="19"/>
+      <c r="D188" s="20"/>
+      <c r="E188" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F188" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A189" s="2">
+      <c r="A189" s="18">
         <v>342804057</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C189" s="1"/>
-      <c r="D189" s="4"/>
-      <c r="E189" s="1"/>
-      <c r="F189" s="1" t="s">
-        <v>7</v>
+      <c r="B189" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C189" s="19"/>
+      <c r="D189" s="20"/>
+      <c r="E189" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F189" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A190" s="2">
+      <c r="A190" s="18">
         <v>413071006</v>
       </c>
-      <c r="B190" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C190" s="1"/>
-      <c r="D190" s="4"/>
-      <c r="E190" s="1"/>
-      <c r="F190" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B190" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C190" s="19"/>
+      <c r="D190" s="20"/>
+      <c r="E190" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F190" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="2">
         <v>415141222</v>
       </c>
@@ -4558,7 +4560,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="2">
         <v>420585540</v>
       </c>
@@ -4574,7 +4576,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="2">
         <v>90200551</v>
       </c>
@@ -4592,7 +4594,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="2">
         <v>408855509</v>
       </c>
@@ -4610,7 +4612,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="2">
         <v>3867409501</v>
       </c>
@@ -4628,7 +4630,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="2">
         <v>4449548647</v>
       </c>
@@ -4644,7 +4646,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="2">
         <v>4723145486</v>
       </c>
@@ -4662,7 +4664,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="2">
         <v>149071</v>
       </c>
@@ -4676,7 +4678,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2">
         <v>6272320</v>
       </c>
@@ -4692,7 +4694,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="2">
         <v>6313531</v>
       </c>
@@ -4708,7 +4710,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="2">
         <v>6340342</v>
       </c>
@@ -4722,7 +4724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="2">
         <v>7231342</v>
       </c>
@@ -4738,7 +4740,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="2">
         <v>11528311</v>
       </c>
@@ -4752,7 +4754,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="2">
         <v>247324</v>
       </c>
@@ -4766,7 +4768,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="2">
         <v>308307</v>
       </c>
@@ -4781,20 +4783,22 @@
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A206" s="2">
+      <c r="A206" s="18">
         <v>2822350</v>
       </c>
-      <c r="B206" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C206" s="1"/>
-      <c r="D206" s="4"/>
-      <c r="E206" s="1"/>
-      <c r="F206" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B206" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C206" s="19"/>
+      <c r="D206" s="20"/>
+      <c r="E206" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F206" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="2">
         <v>3469344</v>
       </c>
@@ -4808,7 +4812,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="2">
         <v>4868250</v>
       </c>
@@ -4822,7 +4826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="2">
         <v>5743095</v>
       </c>
@@ -4836,7 +4840,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="2">
         <v>1450336</v>
       </c>
@@ -4850,7 +4854,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="2">
         <v>1703307</v>
       </c>
@@ -4864,7 +4868,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="2">
         <v>2613352</v>
       </c>
@@ -4880,7 +4884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="2">
         <v>2621533</v>
       </c>
@@ -4894,7 +4898,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="2">
         <v>3708276</v>
       </c>
@@ -4910,7 +4914,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="2">
         <v>8201936582</v>
       </c>
@@ -4924,7 +4928,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="2">
         <v>636304</v>
       </c>
@@ -4940,7 +4944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="2">
         <v>1694200</v>
       </c>
@@ -4954,7 +4958,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="2">
         <v>4889339</v>
       </c>
@@ -4968,7 +4972,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="2">
         <v>5079381</v>
       </c>
@@ -4982,7 +4986,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="2">
         <v>5114390</v>
       </c>
@@ -4996,7 +5000,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="2">
         <v>5265339</v>
       </c>
@@ -5010,7 +5014,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="2">
         <v>11964723</v>
       </c>
@@ -5040,7 +5044,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="2">
         <v>156788730</v>
       </c>
@@ -5056,7 +5060,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="2">
         <v>221921745</v>
       </c>
@@ -5071,20 +5075,22 @@
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A226" s="2">
+      <c r="A226" s="18">
         <v>247862258</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C226" s="1"/>
-      <c r="D226" s="4"/>
-      <c r="E226" s="1"/>
-      <c r="F226" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B226" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C226" s="19"/>
+      <c r="D226" s="20"/>
+      <c r="E226" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F226" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="2">
         <v>260357588</v>
       </c>
@@ -5098,7 +5104,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="2">
         <v>281685770</v>
       </c>
@@ -5112,7 +5118,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="2">
         <v>303117214</v>
       </c>
@@ -5126,7 +5132,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="2">
         <v>345513878</v>
       </c>
@@ -5140,7 +5146,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="2">
         <v>393343766</v>
       </c>
@@ -5155,20 +5161,22 @@
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A232" s="2">
+      <c r="A232" s="18">
         <v>404870406</v>
       </c>
-      <c r="B232" s="1"/>
-      <c r="C232" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D232" s="4"/>
-      <c r="E232" s="1"/>
-      <c r="F232" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B232" s="19"/>
+      <c r="C232" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D232" s="20"/>
+      <c r="E232" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F232" s="19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="2">
         <v>415001994</v>
       </c>
@@ -5184,7 +5192,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" s="2">
         <v>417375638</v>
       </c>
@@ -5200,7 +5208,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" s="2">
         <v>461926709</v>
       </c>
@@ -5214,7 +5222,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" s="2">
         <v>505870568</v>
       </c>
@@ -5244,7 +5252,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" s="2">
         <v>866715029</v>
       </c>
@@ -5258,7 +5266,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" s="2">
         <v>876775202</v>
       </c>
@@ -5275,33 +5283,37 @@
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A240" s="2">
+      <c r="A240" s="18">
         <v>965936953</v>
       </c>
-      <c r="B240" s="1"/>
-      <c r="C240" s="1"/>
-      <c r="D240" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E240" s="1"/>
-      <c r="F240" s="1" t="s">
-        <v>7</v>
+      <c r="B240" s="19"/>
+      <c r="C240" s="19"/>
+      <c r="D240" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E240" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F240" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A241" s="2">
+      <c r="A241" s="18">
         <v>980772796</v>
       </c>
-      <c r="B241" s="1"/>
-      <c r="C241" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D241" s="4" t="s">
+      <c r="B241" s="19"/>
+      <c r="C241" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D241" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="E241" s="1"/>
-      <c r="F241" s="1" t="s">
-        <v>7</v>
+      <c r="E241" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F241" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.3">
@@ -5336,7 +5348,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" s="2">
         <v>1129136876</v>
       </c>
@@ -5350,7 +5362,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" s="2">
         <v>1215211767</v>
       </c>
@@ -5364,7 +5376,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" s="2">
         <v>1270440276</v>
       </c>
@@ -5380,7 +5392,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" s="2">
         <v>1309511101</v>
       </c>
@@ -5412,7 +5424,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" s="2">
         <v>1316735214</v>
       </c>
@@ -5429,17 +5441,19 @@
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A250" s="30">
+      <c r="A250" s="18">
         <v>1327218305</v>
       </c>
-      <c r="B250" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="C250" s="31"/>
-      <c r="D250" s="32"/>
-      <c r="E250" s="31"/>
-      <c r="F250" s="31" t="s">
-        <v>7</v>
+      <c r="B250" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="C250" s="19"/>
+      <c r="D250" s="20"/>
+      <c r="E250" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="F250" s="19" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.3">
@@ -5492,7 +5506,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="2">
         <v>1752772733</v>
       </c>
@@ -5538,7 +5552,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="2">
         <v>2346482285</v>
       </c>
@@ -5570,7 +5584,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="2">
         <v>2467922480</v>
       </c>
@@ -5650,7 +5664,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="2">
         <v>2936656729</v>
       </c>
@@ -5697,6 +5711,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F266" xr:uid="{834A0C64-4F07-424E-993E-2EA5E6BA9836}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="SIM"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="A2:F2">
     <cfRule type="cellIs" dxfId="0" priority="2" stopIfTrue="1" operator="greaterThan">
       <formula>$F$2="SIM"</formula>
@@ -5935,53 +5956,53 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="37">
+      <c r="A3" s="21">
         <v>2</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="40">
-        <v>6</v>
+      <c r="D3" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="29">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37">
+      <c r="A4" s="21">
         <v>3</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="40">
-        <v>6</v>
+      <c r="D4" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="29">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37">
+      <c r="A5" s="21">
         <v>4</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="40">
+      <c r="D5" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="29">
         <v>6</v>
       </c>
     </row>
@@ -6054,20 +6075,20 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="37">
+      <c r="A10" s="21">
         <v>9</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="40">
-        <v>7</v>
+      <c r="D10" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="29">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
@@ -6172,54 +6193,54 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="25">
+    <row r="17" spans="1:5" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="21">
         <v>16</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="28">
-        <v>2</v>
+      <c r="D17" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="29">
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="37">
+      <c r="A18" s="21">
         <v>17</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="39" t="s">
+      <c r="C18" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="E18" s="40">
+      <c r="D18" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="29">
         <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="33">
+      <c r="A19" s="21">
         <v>18</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B19" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="35" t="s">
+      <c r="C19" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="D19" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="36">
+      <c r="D19" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="29">
         <v>3</v>
       </c>
     </row>
@@ -6237,92 +6258,92 @@
         <v>39</v>
       </c>
       <c r="E20" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A21" s="25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="21">
         <v>20</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="21">
+        <v>21</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="33">
+        <v>22</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A22" s="41">
-        <v>21</v>
-      </c>
-      <c r="B22" s="42" t="s">
+      <c r="E23" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="33">
+        <v>23</v>
+      </c>
+      <c r="B24" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="41" t="s">
+      <c r="C24" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="E22" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="41">
-        <v>22</v>
-      </c>
-      <c r="B23" s="42" t="s">
+      <c r="E24" s="36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="33">
+        <v>24</v>
+      </c>
+      <c r="B25" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="43" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="41" t="s">
+      <c r="C25" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="E23" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="41">
-        <v>23</v>
-      </c>
-      <c r="B24" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="C24" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="41">
-        <v>24</v>
-      </c>
-      <c r="B25" s="42" t="s">
-        <v>66</v>
-      </c>
-      <c r="C25" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="44">
-        <v>1</v>
+      <c r="E25" s="36">
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
@@ -6356,7 +6377,7 @@
         <v>39</v>
       </c>
       <c r="E27" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
@@ -6373,7 +6394,7 @@
         <v>39</v>
       </c>
       <c r="E28" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -6522,7 +6543,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
-        <v>0.69930555555555551</v>
+        <v>0.47916666666666669</v>
       </c>
       <c r="B5" s="13">
         <v>46254</v>
@@ -6531,16 +6552,16 @@
         <v>0</v>
       </c>
       <c r="D5" s="14">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E5" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G5" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H5" s="15">
         <f>C5+D5+E5+G5+F5</f>

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70E7D14-7EC5-4C72-AFE3-0E3C07279779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BBF23C-483B-423F-822B-127EBFE39001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Massa_HML_B31_FLUXO_INTEGRADO" sheetId="3" r:id="rId1"/>
@@ -6296,20 +6296,20 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="33">
+      <c r="A23" s="21">
         <v>22</v>
       </c>
-      <c r="B23" s="34" t="s">
+      <c r="B23" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="35" t="s">
+      <c r="C23" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="D23" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="36">
-        <v>2</v>
+      <c r="D23" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="29">
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
@@ -6360,7 +6360,7 @@
         <v>39</v>
       </c>
       <c r="E26" s="28">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
@@ -6552,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" s="14">
         <v>0</v>
@@ -6561,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H5" s="15">
         <f>C5+D5+E5+G5+F5</f>

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9BBF23C-483B-423F-822B-127EBFE39001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5238F3-D575-4B89-BC64-AE9CF42D76A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Massa_HML_B31_FLUXO_INTEGRADO" sheetId="3" r:id="rId1"/>
@@ -6245,20 +6245,20 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="72" x14ac:dyDescent="0.3">
-      <c r="A20" s="25">
+      <c r="A20" s="21">
         <v>19</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="D20" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="28">
-        <v>2</v>
+      <c r="D20" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" s="29">
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
@@ -6295,7 +6295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="21">
         <v>22</v>
       </c>
@@ -6312,20 +6312,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="33">
+    <row r="24" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="21">
         <v>23</v>
       </c>
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="C24" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D24" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="E24" s="36">
+      <c r="D24" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="29">
         <v>2</v>
       </c>
     </row>
@@ -6346,55 +6346,55 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="25">
+    <row r="26" spans="1:5" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="21">
         <v>25</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E26" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="25">
+      <c r="D26" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="21">
         <v>26</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="D27" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="25">
+      <c r="D27" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="21">
         <v>27</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="D28" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="E28" s="28">
-        <v>2</v>
+      <c r="D28" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="29">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -6552,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="14">
         <v>0</v>
@@ -6561,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" s="15">
         <f>C5+D5+E5+G5+F5</f>

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5238F3-D575-4B89-BC64-AE9CF42D76A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B605C3-3F61-49EF-B6F2-968E4C751D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Massa_HML_B31_FLUXO_INTEGRADO" sheetId="3" r:id="rId1"/>
@@ -5910,7 +5910,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A07569E-5BDC-415E-ABD1-103C61B67D37}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5938,7 +5937,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="21">
         <v>1</v>
       </c>
@@ -5955,7 +5954,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="21">
         <v>2</v>
       </c>
@@ -5972,7 +5971,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="21">
         <v>3</v>
       </c>
@@ -5989,7 +5988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="21">
         <v>4</v>
       </c>
@@ -6006,7 +6005,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="21">
         <v>5</v>
       </c>
@@ -6023,7 +6022,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="21">
         <v>6</v>
       </c>
@@ -6040,7 +6039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="21">
         <v>7</v>
       </c>
@@ -6057,7 +6056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="21">
         <v>8</v>
       </c>
@@ -6074,7 +6073,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="21">
         <v>9</v>
       </c>
@@ -6108,7 +6107,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="21">
         <v>11</v>
       </c>
@@ -6125,7 +6124,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="21">
         <v>12</v>
       </c>
@@ -6142,7 +6141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A14" s="21">
         <v>13</v>
       </c>
@@ -6159,7 +6158,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="21">
         <v>14</v>
       </c>
@@ -6176,7 +6175,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="21">
         <v>15</v>
       </c>
@@ -6193,7 +6192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="21">
         <v>16</v>
       </c>
@@ -6210,7 +6209,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="21">
         <v>17</v>
       </c>
@@ -6227,7 +6226,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A19" s="21">
         <v>18</v>
       </c>
@@ -6261,7 +6260,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A21" s="21">
         <v>20</v>
       </c>
@@ -6278,7 +6277,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="72" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" s="21">
         <v>21</v>
       </c>
@@ -6295,7 +6294,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="21">
         <v>22</v>
       </c>
@@ -6312,7 +6311,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="21">
         <v>23</v>
       </c>
@@ -6346,7 +6345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A26" s="21">
         <v>25</v>
       </c>
@@ -6363,7 +6362,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A27" s="21">
         <v>26</v>
       </c>
@@ -6380,7 +6379,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A28" s="21">
         <v>27</v>
       </c>
@@ -6398,13 +6397,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="D1:D28" xr:uid="{9A07569E-5BDC-415E-ABD1-103C61B67D37}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="EM TESTE"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="D1:D28" xr:uid="{9A07569E-5BDC-415E-ABD1-103C61B67D37}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -6543,25 +6536,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="12">
-        <v>0.47916666666666669</v>
+        <v>0.625</v>
       </c>
       <c r="B5" s="13">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="C5" s="14">
         <v>0</v>
       </c>
       <c r="D5" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E5" s="14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="14">
         <v>0</v>
       </c>
       <c r="G5" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H5" s="15">
         <f>C5+D5+E5+G5+F5</f>

--- a/fluxo-integrado/Massa_CPFs_FPSE.xlsx
+++ b/fluxo-integrado/Massa_CPFs_FPSE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B605C3-3F61-49EF-B6F2-968E4C751D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F04A8A-9EA2-47BE-9448-392D31835AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{59B77761-AE3C-4E52-A7E7-6436E081B1B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Massa_HML_B31_FLUXO_INTEGRADO" sheetId="3" r:id="rId1"/>
@@ -464,7 +464,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -677,12 +677,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -914,7 +908,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -980,16 +974,6 @@
     <xf numFmtId="164" fontId="0" fillId="38" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="38" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -6325,24 +6309,24 @@
         <v>35</v>
       </c>
       <c r="E24" s="29">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="33">
+      <c r="A25" s="21">
         <v>24</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C25" s="35" t="s">
+      <c r="C25" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="36">
-        <v>2</v>
+      <c r="D25" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="29">
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
@@ -6545,10 +6529,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="14">
         <v>0</v>
